--- a/data_understanding/data/argentina/entidad_next_partido.xlsx
+++ b/data_understanding/data/argentina/entidad_next_partido.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10514"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nachomondino/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07246D1-B221-D54F-9524-FD9AF72E2B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48BA7050-17B6-F742-90A3-3D2387E75FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1927" uniqueCount="1083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="931">
   <si>
     <t>id</t>
   </si>
@@ -59,78 +59,12 @@
     <t>equipo_vis</t>
   </si>
   <si>
-    <t>goles_loc</t>
-  </si>
-  <si>
-    <t>goles_vis</t>
-  </si>
-  <si>
     <t>arbitro</t>
   </si>
   <si>
     <t>cancha</t>
   </si>
   <si>
-    <t>posesion_loc</t>
-  </si>
-  <si>
-    <t>posesion_vis</t>
-  </si>
-  <si>
-    <t>remates_loc</t>
-  </si>
-  <si>
-    <t>remates_vis</t>
-  </si>
-  <si>
-    <t>remates_a_puerta_loc</t>
-  </si>
-  <si>
-    <t>remates_a_puerta_vis</t>
-  </si>
-  <si>
-    <t>tarjetas_amarillas_loc</t>
-  </si>
-  <si>
-    <t>tarjetas_amarillas_vis</t>
-  </si>
-  <si>
-    <t>faltas_loc</t>
-  </si>
-  <si>
-    <t>faltas_vis</t>
-  </si>
-  <si>
-    <t>pases_loc</t>
-  </si>
-  <si>
-    <t>pases_vis</t>
-  </si>
-  <si>
-    <t>pases_comp_loc</t>
-  </si>
-  <si>
-    <t>pases_comp_vis</t>
-  </si>
-  <si>
-    <t>offsides_loc</t>
-  </si>
-  <si>
-    <t>offsides_vis</t>
-  </si>
-  <si>
-    <t>ataques_loc</t>
-  </si>
-  <si>
-    <t>ataques_vis</t>
-  </si>
-  <si>
-    <t>ataques_pelig_loc</t>
-  </si>
-  <si>
-    <t>ataques_pelig_vis</t>
-  </si>
-  <si>
     <t>jug_tit_loc_1</t>
   </si>
   <si>
@@ -362,48 +296,12 @@
     <t>Racing Club</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Trucco S. (Arg)</t>
   </si>
   <si>
     <t>Estadio Presidente Peron (Córdoba)</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>122</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>roffo manuel</t>
   </si>
   <si>
@@ -572,27 +470,6 @@
     <t>Estadio José Amalfitani (Buenos Aires)</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>126</t>
-  </si>
-  <si>
-    <t>158</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
     <t>gomez gaston</t>
   </si>
   <si>
@@ -758,27 +635,12 @@
     <t>River Plate</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>Tello F. (Arg)</t>
   </si>
   <si>
     <t>Estadio Florencio Sola (Buenos Aires)</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
     <t>cambeses facundo</t>
   </si>
   <si>
@@ -959,24 +821,6 @@
     <t>Estadio Pedro Bidegain (Buenos Aires)</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>130</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
     <t>batalla augusto</t>
   </si>
   <si>
@@ -1148,24 +992,6 @@
     <t>Estadio Marcelo Bielsa (Rosario)</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>hoyos lucas</t>
   </si>
   <si>
@@ -1340,18 +1166,6 @@
     <t>Estadio Mario Alberto Kempes (Córdoba)</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>herrera guido</t>
   </si>
   <si>
@@ -1520,15 +1334,6 @@
     <t>Estadio Alberto J. Armando (Buenos Aires)</t>
   </si>
   <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
     <t>garcia javier</t>
   </si>
   <si>
@@ -1691,12 +1496,6 @@
     <t>Estadio Ciudad de Vicente López (Buenos Aires)</t>
   </si>
   <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
     <t>macagno ramiro</t>
   </si>
   <si>
@@ -1880,15 +1679,6 @@
     <t>Estadio Libertadores de América (Avellaneda)</t>
   </si>
   <si>
-    <t>117</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
     <t>rey rodrigo</t>
   </si>
   <si>
@@ -2069,15 +1859,6 @@
     <t>Claudio Fabian Tapia (Barracas)</t>
   </si>
   <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>79</t>
-  </si>
-  <si>
     <t>desabato andres</t>
   </si>
   <si>
@@ -2243,33 +2024,6 @@
     <t>Estadio Ciudad de Lanús – Néstor Díaz Pérez (Lanús)</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>379</t>
-  </si>
-  <si>
-    <t>515</t>
-  </si>
-  <si>
-    <t>314</t>
-  </si>
-  <si>
-    <t>422</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>138</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>marchiori tomas</t>
   </si>
   <si>
@@ -2363,24 +2117,6 @@
     <t>Estadio Malvinas Argentinas (Mendoza)</t>
   </si>
   <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>310</t>
-  </si>
-  <si>
-    <t>233</t>
-  </si>
-  <si>
-    <t>123</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
     <t>rodriguez diego</t>
   </si>
   <si>
@@ -2477,27 +2213,6 @@
     <t>Herrera D. (Arg)</t>
   </si>
   <si>
-    <t>432</t>
-  </si>
-  <si>
-    <t>424</t>
-  </si>
-  <si>
-    <t>355</t>
-  </si>
-  <si>
-    <t>337</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>88</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
     <t>chicco ignacio</t>
   </si>
   <si>
@@ -2591,21 +2306,6 @@
     <t>Estadio 15 de Abril (Santa Fe)</t>
   </si>
   <si>
-    <t>287</t>
-  </si>
-  <si>
-    <t>279</t>
-  </si>
-  <si>
-    <t>199</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>220</t>
-  </si>
-  <si>
     <t>durso tomas</t>
   </si>
   <si>
@@ -2699,18 +2399,6 @@
     <t>Estadio Juan Domingo Perón (Avellaneda)</t>
   </si>
   <si>
-    <t>499</t>
-  </si>
-  <si>
-    <t>285</t>
-  </si>
-  <si>
-    <t>393</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
     <t>arias gabriel</t>
   </si>
   <si>
@@ -2744,24 +2432,6 @@
     <t>Estadio Unico Madre de Ciudades (Santiago del Estero)</t>
   </si>
   <si>
-    <t>213</t>
-  </si>
-  <si>
-    <t>491</t>
-  </si>
-  <si>
-    <t>165</t>
-  </si>
-  <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>132</t>
-  </si>
-  <si>
     <t>chavez lucas</t>
   </si>
   <si>
@@ -2849,30 +2519,6 @@
     <t>Estadio Gigante de Arroyito (Rosario)</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>485</t>
-  </si>
-  <si>
-    <t>232</t>
-  </si>
-  <si>
-    <t>386</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
     <t>albertengo lucas</t>
   </si>
   <si>
@@ -2891,18 +2537,6 @@
     <t>Estadio Julio Cesar Villagra (Córdoba)</t>
   </si>
   <si>
-    <t>258</t>
-  </si>
-  <si>
-    <t>455</t>
-  </si>
-  <si>
-    <t>185</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
     <t>losada nahuel</t>
   </si>
   <si>
@@ -2999,24 +2633,6 @@
     <t>Estadio Diego Armando Maradona (Buenos Aires)</t>
   </si>
   <si>
-    <t>316</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>69</t>
-  </si>
-  <si>
     <t>mac allister kevin</t>
   </si>
   <si>
@@ -3038,21 +2654,6 @@
     <t>Estadio José Dellagiovanna (Buenos Aires)</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>360</t>
-  </si>
-  <si>
-    <t>409</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
     <t>barrera diego</t>
   </si>
   <si>
@@ -3074,30 +2675,6 @@
     <t>Estadio Jorge Luis Hirschi (La Plata)</t>
   </si>
   <si>
-    <t>494</t>
-  </si>
-  <si>
-    <t>382</t>
-  </si>
-  <si>
-    <t>407</t>
-  </si>
-  <si>
-    <t>304</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>118</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>andujar mariano</t>
   </si>
   <si>
@@ -3197,24 +2774,6 @@
     <t>Estadio Julio Humberto Grondona (Avellaneda)</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>708</t>
-  </si>
-  <si>
-    <t>147</t>
-  </si>
-  <si>
-    <t>639</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
     <t>sporle adrian</t>
   </si>
   <si>
@@ -3255,21 +2814,6 @@
   </si>
   <si>
     <t>Estadio Eva Peron (Junin)</t>
-  </si>
-  <si>
-    <t>209</t>
-  </si>
-  <si>
-    <t>524</t>
-  </si>
-  <si>
-    <t>142</t>
-  </si>
-  <si>
-    <t>442</t>
-  </si>
-  <si>
-    <t>30</t>
   </si>
   <si>
     <t>femia nicolas</t>
@@ -3341,13 +2885,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3650,7 +3193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CY76"/>
+  <dimension ref="A1:CC76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
@@ -3660,97 +3203,78 @@
     <col min="5" max="5" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="43.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="15" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="16" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="43" width="22" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="18" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="15" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="19" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="18" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="19" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="71" max="72" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="79" max="79" width="15" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="81" max="81" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="82" max="83" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="8" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="86" max="86" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="87" max="87" width="16" bestFit="1" customWidth="1"/>
-    <col min="88" max="88" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="13.83203125" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="93" max="93" width="16" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="102" max="102" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="103" max="103" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="22" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="18" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="19" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="49" max="50" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="15" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="60" max="61" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="8" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="16" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="16" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="79" max="79" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="81" max="81" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3994,85 +3518,19 @@
       <c r="CC1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:81" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="B2" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="C2" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="D2" t="s">
         <v>84</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="CN1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="CS1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="CT1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="CU1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="CV1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="CW1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="CX1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="CY1" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:103" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D2" t="s">
-        <v>106</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -4081,246 +3539,192 @@
         <v>45089.90625</v>
       </c>
       <c r="G2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N2" t="s">
+        <v>92</v>
+      </c>
+      <c r="O2" t="s">
+        <v>93</v>
+      </c>
+      <c r="P2" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R2" t="s">
+        <v>96</v>
+      </c>
+      <c r="S2" t="s">
+        <v>97</v>
+      </c>
+      <c r="T2" t="s">
+        <v>98</v>
+      </c>
+      <c r="U2" t="s">
+        <v>99</v>
+      </c>
+      <c r="V2" t="s">
+        <v>100</v>
+      </c>
+      <c r="W2" t="s">
+        <v>101</v>
+      </c>
+      <c r="X2" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>106</v>
+      </c>
+      <c r="AC2" t="s">
         <v>107</v>
       </c>
-      <c r="H2" t="s">
+      <c r="AD2" t="s">
         <v>108</v>
       </c>
-      <c r="I2" t="s">
+      <c r="AE2" t="s">
         <v>109</v>
       </c>
-      <c r="J2" t="s">
-        <v>109</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="AF2" t="s">
         <v>110</v>
       </c>
-      <c r="L2" t="s">
+      <c r="AG2" t="s">
         <v>111</v>
       </c>
-      <c r="M2" s="3">
-        <v>35</v>
-      </c>
-      <c r="N2" s="3">
-        <v>65</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="AH2" t="s">
         <v>112</v>
       </c>
-      <c r="P2" t="s">
+      <c r="AI2" t="s">
         <v>113</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="AJ2" t="s">
         <v>114</v>
       </c>
-      <c r="R2" t="s">
+      <c r="AK2" t="s">
         <v>115</v>
       </c>
-      <c r="S2" t="s">
+      <c r="AL2" t="s">
         <v>116</v>
       </c>
-      <c r="T2" t="s">
-        <v>114</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="AM2" t="s">
         <v>117</v>
       </c>
-      <c r="V2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="AN2" t="s">
         <v>118</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AO2" t="s">
         <v>119</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AP2" t="s">
         <v>120</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AQ2" t="s">
         <v>121</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AR2" t="s">
         <v>122</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AS2" t="s">
         <v>123</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AT2" t="s">
         <v>124</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AU2" t="s">
         <v>125</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AV2" t="s">
         <v>126</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AW2" t="s">
         <v>127</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AX2" t="s">
         <v>128</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AY2" t="s">
         <v>129</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AZ2" t="s">
         <v>130</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="BA2" t="s">
         <v>131</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="BB2" t="s">
         <v>132</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="BC2" t="s">
         <v>133</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="BD2" t="s">
         <v>134</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="BE2" t="s">
         <v>135</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="BF2" t="s">
         <v>136</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="BG2" t="s">
         <v>137</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="BH2" t="s">
         <v>138</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="BI2" t="s">
         <v>139</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BJ2">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="BK2">
+        <v>3.1</v>
+      </c>
+      <c r="BL2">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:81" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>140</v>
       </c>
-      <c r="AY2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>142</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>143</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>144</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>145</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>146</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>147</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>149</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>151</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>152</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>153</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>154</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>155</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>156</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>157</v>
-      </c>
-      <c r="BP2" t="s">
-        <v>158</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>159</v>
-      </c>
-      <c r="BR2" t="s">
-        <v>160</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>161</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>162</v>
-      </c>
-      <c r="BU2" t="s">
-        <v>163</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>164</v>
-      </c>
-      <c r="BW2" t="s">
-        <v>165</v>
-      </c>
-      <c r="BX2" t="s">
-        <v>166</v>
-      </c>
-      <c r="BY2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BZ2" t="s">
-        <v>168</v>
-      </c>
-      <c r="CA2" t="s">
-        <v>169</v>
-      </c>
-      <c r="CB2" t="s">
-        <v>170</v>
-      </c>
-      <c r="CC2" t="s">
-        <v>171</v>
-      </c>
-      <c r="CD2" t="s">
-        <v>172</v>
-      </c>
-      <c r="CE2" t="s">
-        <v>173</v>
-      </c>
-      <c r="CF2">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="CG2">
-        <v>3.1</v>
-      </c>
-      <c r="CH2">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:103" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>174</v>
-      </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -4329,249 +3733,195 @@
         <v>45089.90625</v>
       </c>
       <c r="G3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K3" t="s">
+        <v>145</v>
+      </c>
+      <c r="L3" t="s">
+        <v>146</v>
+      </c>
+      <c r="M3" t="s">
+        <v>147</v>
+      </c>
+      <c r="N3" t="s">
+        <v>148</v>
+      </c>
+      <c r="O3" t="s">
+        <v>149</v>
+      </c>
+      <c r="P3" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>151</v>
+      </c>
+      <c r="R3" t="s">
+        <v>152</v>
+      </c>
+      <c r="S3" t="s">
+        <v>153</v>
+      </c>
+      <c r="T3" t="s">
+        <v>154</v>
+      </c>
+      <c r="U3" t="s">
+        <v>155</v>
+      </c>
+      <c r="V3" t="s">
+        <v>156</v>
+      </c>
+      <c r="W3" t="s">
+        <v>157</v>
+      </c>
+      <c r="X3" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>162</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>164</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>166</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>172</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>173</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>174</v>
+      </c>
+      <c r="AP3" t="s">
         <v>175</v>
       </c>
-      <c r="H3" t="s">
+      <c r="AQ3" t="s">
         <v>176</v>
       </c>
-      <c r="I3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J3" t="s">
-        <v>109</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="AR3" t="s">
         <v>177</v>
       </c>
-      <c r="L3" t="s">
+      <c r="AS3" t="s">
         <v>178</v>
       </c>
-      <c r="M3" s="3">
-        <v>39</v>
-      </c>
-      <c r="N3" s="3">
-        <v>61</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="AT3" t="s">
         <v>179</v>
       </c>
-      <c r="P3" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>116</v>
-      </c>
-      <c r="R3" t="s">
-        <v>116</v>
-      </c>
-      <c r="S3" t="s">
-        <v>116</v>
-      </c>
-      <c r="T3" t="s">
-        <v>114</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="AU3" t="s">
         <v>180</v>
       </c>
-      <c r="V3" t="s">
+      <c r="AV3" t="s">
         <v>181</v>
       </c>
-      <c r="AA3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>109</v>
-      </c>
-      <c r="AC3" t="s">
+      <c r="AW3" t="s">
         <v>182</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AX3" t="s">
         <v>183</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AY3" t="s">
         <v>184</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AZ3" t="s">
         <v>185</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="BA3" t="s">
         <v>186</v>
       </c>
-      <c r="AH3" t="s">
+      <c r="BB3" t="s">
         <v>187</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="BC3" t="s">
         <v>188</v>
       </c>
-      <c r="AJ3" t="s">
+      <c r="BD3" t="s">
         <v>189</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="BE3" t="s">
         <v>190</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="BH3" t="s">
         <v>191</v>
       </c>
-      <c r="AM3" t="s">
+      <c r="BI3" t="s">
         <v>192</v>
       </c>
-      <c r="AN3" t="s">
+      <c r="BJ3">
+        <v>2.88</v>
+      </c>
+      <c r="BK3">
+        <v>2.9</v>
+      </c>
+      <c r="BL3">
+        <v>2.5</v>
+      </c>
+      <c r="BM3" t="s">
         <v>193</v>
       </c>
-      <c r="AO3" t="s">
+      <c r="BN3" t="s">
         <v>194</v>
       </c>
-      <c r="AP3" t="s">
+      <c r="BO3" t="s">
         <v>195</v>
       </c>
-      <c r="AQ3" t="s">
+      <c r="BP3" t="s">
         <v>196</v>
       </c>
-      <c r="AR3" t="s">
+    </row>
+    <row r="4" spans="1:81" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>197</v>
       </c>
-      <c r="AS3" t="s">
-        <v>198</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>199</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>200</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>201</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>202</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>203</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>204</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>205</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>206</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>207</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>208</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>209</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>210</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>211</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>212</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>213</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>214</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>215</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>216</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>217</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>218</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>219</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>220</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>221</v>
-      </c>
-      <c r="BR3" t="s">
-        <v>222</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>223</v>
-      </c>
-      <c r="BT3" t="s">
-        <v>224</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>225</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>226</v>
-      </c>
-      <c r="BW3" t="s">
-        <v>227</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>228</v>
-      </c>
-      <c r="BY3" t="s">
-        <v>229</v>
-      </c>
-      <c r="BZ3" t="s">
-        <v>230</v>
-      </c>
-      <c r="CA3" t="s">
-        <v>231</v>
-      </c>
-      <c r="CD3" t="s">
-        <v>232</v>
-      </c>
-      <c r="CE3" t="s">
-        <v>233</v>
-      </c>
-      <c r="CF3">
-        <v>2.88</v>
-      </c>
-      <c r="CG3">
-        <v>2.9</v>
-      </c>
-      <c r="CH3">
-        <v>2.5</v>
-      </c>
-      <c r="CI3" t="s">
-        <v>234</v>
-      </c>
-      <c r="CJ3" t="s">
-        <v>235</v>
-      </c>
-      <c r="CK3" t="s">
-        <v>236</v>
-      </c>
-      <c r="CL3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="4" spans="1:103" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>238</v>
-      </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -4580,258 +3930,204 @@
         <v>45089.802083333343</v>
       </c>
       <c r="G4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I4" t="s">
+        <v>200</v>
+      </c>
+      <c r="J4" t="s">
+        <v>201</v>
+      </c>
+      <c r="K4" t="s">
+        <v>202</v>
+      </c>
+      <c r="L4" t="s">
+        <v>203</v>
+      </c>
+      <c r="M4" t="s">
+        <v>204</v>
+      </c>
+      <c r="N4" t="s">
+        <v>205</v>
+      </c>
+      <c r="O4" t="s">
+        <v>206</v>
+      </c>
+      <c r="P4" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>208</v>
+      </c>
+      <c r="R4" t="s">
+        <v>209</v>
+      </c>
+      <c r="S4" t="s">
+        <v>210</v>
+      </c>
+      <c r="T4" t="s">
+        <v>211</v>
+      </c>
+      <c r="U4" t="s">
+        <v>212</v>
+      </c>
+      <c r="V4" t="s">
+        <v>213</v>
+      </c>
+      <c r="W4" t="s">
+        <v>214</v>
+      </c>
+      <c r="X4" t="s">
+        <v>215</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>216</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>217</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>218</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>219</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>220</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>221</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>222</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>223</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>224</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>225</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>227</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>228</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>229</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>230</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>231</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>232</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>233</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>234</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>235</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>236</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>237</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>238</v>
+      </c>
+      <c r="AV4" t="s">
         <v>239</v>
       </c>
-      <c r="H4" t="s">
+      <c r="AW4" t="s">
         <v>240</v>
       </c>
-      <c r="I4" t="s">
-        <v>109</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="AX4" t="s">
         <v>241</v>
       </c>
-      <c r="K4" t="s">
+      <c r="AY4" t="s">
         <v>242</v>
       </c>
-      <c r="L4" t="s">
+      <c r="AZ4" t="s">
         <v>243</v>
       </c>
-      <c r="M4" s="3">
-        <v>34</v>
-      </c>
-      <c r="N4" s="3">
-        <v>66</v>
-      </c>
-      <c r="O4" t="s">
-        <v>179</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="BA4" t="s">
         <v>244</v>
       </c>
-      <c r="Q4" t="s">
-        <v>114</v>
-      </c>
-      <c r="R4" t="s">
-        <v>115</v>
-      </c>
-      <c r="S4" t="s">
-        <v>109</v>
-      </c>
-      <c r="T4" t="s">
-        <v>109</v>
-      </c>
-      <c r="U4" t="s">
-        <v>112</v>
-      </c>
-      <c r="V4" t="s">
-        <v>180</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>116</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>120</v>
-      </c>
-      <c r="AD4" t="s">
+      <c r="BB4" t="s">
         <v>245</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="BC4" t="s">
         <v>246</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="BD4" t="s">
         <v>247</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="BE4" t="s">
         <v>248</v>
       </c>
-      <c r="AH4" t="s">
+      <c r="BF4" t="s">
         <v>249</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="BG4" t="s">
         <v>250</v>
       </c>
-      <c r="AJ4" t="s">
+      <c r="BH4" t="s">
         <v>251</v>
       </c>
-      <c r="AK4" t="s">
+      <c r="BI4" t="s">
         <v>252</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="BJ4">
+        <v>3.75</v>
+      </c>
+      <c r="BK4">
+        <v>3.4</v>
+      </c>
+      <c r="BL4">
+        <v>1.8</v>
+      </c>
+      <c r="BN4" t="s">
         <v>253</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="BO4" t="s">
         <v>254</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="BP4" t="s">
         <v>255</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="BQ4" t="s">
         <v>256</v>
       </c>
-      <c r="AP4" t="s">
+    </row>
+    <row r="5" spans="1:81" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>257</v>
       </c>
-      <c r="AQ4" t="s">
-        <v>258</v>
-      </c>
-      <c r="AR4" t="s">
-        <v>259</v>
-      </c>
-      <c r="AS4" t="s">
-        <v>260</v>
-      </c>
-      <c r="AT4" t="s">
-        <v>261</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>262</v>
-      </c>
-      <c r="AV4" t="s">
-        <v>263</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>264</v>
-      </c>
-      <c r="AX4" t="s">
-        <v>265</v>
-      </c>
-      <c r="AY4" t="s">
-        <v>266</v>
-      </c>
-      <c r="AZ4" t="s">
-        <v>267</v>
-      </c>
-      <c r="BA4" t="s">
-        <v>268</v>
-      </c>
-      <c r="BB4" t="s">
-        <v>269</v>
-      </c>
-      <c r="BC4" t="s">
-        <v>270</v>
-      </c>
-      <c r="BD4" t="s">
-        <v>271</v>
-      </c>
-      <c r="BE4" t="s">
-        <v>272</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>273</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>274</v>
-      </c>
-      <c r="BH4" t="s">
-        <v>275</v>
-      </c>
-      <c r="BI4" t="s">
-        <v>276</v>
-      </c>
-      <c r="BJ4" t="s">
-        <v>277</v>
-      </c>
-      <c r="BK4" t="s">
-        <v>278</v>
-      </c>
-      <c r="BL4" t="s">
-        <v>279</v>
-      </c>
-      <c r="BM4" t="s">
-        <v>280</v>
-      </c>
-      <c r="BN4" t="s">
-        <v>281</v>
-      </c>
-      <c r="BO4" t="s">
-        <v>282</v>
-      </c>
-      <c r="BP4" t="s">
-        <v>283</v>
-      </c>
-      <c r="BQ4" t="s">
-        <v>284</v>
-      </c>
-      <c r="BR4" t="s">
-        <v>285</v>
-      </c>
-      <c r="BS4" t="s">
-        <v>286</v>
-      </c>
-      <c r="BT4" t="s">
-        <v>287</v>
-      </c>
-      <c r="BU4" t="s">
-        <v>288</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>289</v>
-      </c>
-      <c r="BW4" t="s">
-        <v>290</v>
-      </c>
-      <c r="BX4" t="s">
-        <v>291</v>
-      </c>
-      <c r="BY4" t="s">
-        <v>292</v>
-      </c>
-      <c r="BZ4" t="s">
-        <v>293</v>
-      </c>
-      <c r="CA4" t="s">
-        <v>294</v>
-      </c>
-      <c r="CB4" t="s">
-        <v>295</v>
-      </c>
-      <c r="CC4" t="s">
-        <v>296</v>
-      </c>
-      <c r="CD4" t="s">
-        <v>297</v>
-      </c>
-      <c r="CE4" t="s">
-        <v>298</v>
-      </c>
-      <c r="CF4">
-        <v>3.75</v>
-      </c>
-      <c r="CG4">
-        <v>3.4</v>
-      </c>
-      <c r="CH4">
-        <v>1.8</v>
-      </c>
-      <c r="CJ4" t="s">
-        <v>299</v>
-      </c>
-      <c r="CK4" t="s">
-        <v>300</v>
-      </c>
-      <c r="CL4" t="s">
-        <v>301</v>
-      </c>
-      <c r="CM4" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="5" spans="1:103" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>303</v>
-      </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -4840,249 +4136,195 @@
         <v>45089.708333333343</v>
       </c>
       <c r="G5" t="s">
+        <v>258</v>
+      </c>
+      <c r="H5" t="s">
+        <v>259</v>
+      </c>
+      <c r="I5" t="s">
+        <v>260</v>
+      </c>
+      <c r="J5" t="s">
+        <v>261</v>
+      </c>
+      <c r="K5" t="s">
+        <v>262</v>
+      </c>
+      <c r="L5" t="s">
+        <v>263</v>
+      </c>
+      <c r="M5" t="s">
+        <v>264</v>
+      </c>
+      <c r="N5" t="s">
+        <v>265</v>
+      </c>
+      <c r="O5" t="s">
+        <v>266</v>
+      </c>
+      <c r="P5" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>268</v>
+      </c>
+      <c r="R5" t="s">
+        <v>269</v>
+      </c>
+      <c r="S5" t="s">
+        <v>270</v>
+      </c>
+      <c r="T5" t="s">
+        <v>271</v>
+      </c>
+      <c r="U5" t="s">
+        <v>272</v>
+      </c>
+      <c r="V5" t="s">
+        <v>273</v>
+      </c>
+      <c r="W5" t="s">
+        <v>274</v>
+      </c>
+      <c r="X5" t="s">
+        <v>275</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>277</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>278</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>279</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>280</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>281</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>282</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>283</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>284</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>285</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>286</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>287</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>288</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>289</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>290</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>291</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>292</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>293</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>294</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>295</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>296</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>297</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>298</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>299</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>300</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>302</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>303</v>
+      </c>
+      <c r="BE5" t="s">
         <v>304</v>
       </c>
-      <c r="H5" t="s">
+      <c r="BF5" t="s">
         <v>305</v>
       </c>
-      <c r="I5" t="s">
-        <v>118</v>
-      </c>
-      <c r="J5" t="s">
-        <v>118</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="BH5" t="s">
         <v>306</v>
       </c>
-      <c r="L5" t="s">
+      <c r="BI5" t="s">
         <v>307</v>
       </c>
-      <c r="M5" s="3">
-        <v>60</v>
-      </c>
-      <c r="N5" s="3">
-        <v>40</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="BJ5">
+        <v>1.8</v>
+      </c>
+      <c r="BK5">
+        <v>3.1</v>
+      </c>
+      <c r="BL5">
+        <v>4.75</v>
+      </c>
+      <c r="BN5" t="s">
         <v>308</v>
       </c>
-      <c r="P5" t="s">
+      <c r="BO5" t="s">
         <v>309</v>
       </c>
-      <c r="Q5" t="s">
-        <v>309</v>
-      </c>
-      <c r="R5" t="s">
-        <v>109</v>
-      </c>
-      <c r="S5" t="s">
-        <v>109</v>
-      </c>
-      <c r="T5" t="s">
-        <v>241</v>
-      </c>
-      <c r="U5" t="s">
-        <v>179</v>
-      </c>
-      <c r="V5" t="s">
-        <v>181</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>109</v>
-      </c>
-      <c r="AC5" t="s">
+      <c r="BR5" t="s">
         <v>310</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="BS5" t="s">
         <v>311</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="BT5" t="s">
         <v>312</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="BU5" t="s">
         <v>313</v>
       </c>
-      <c r="AG5" t="s">
+    </row>
+    <row r="6" spans="1:81" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>314</v>
       </c>
-      <c r="AH5" t="s">
-        <v>315</v>
-      </c>
-      <c r="AI5" t="s">
-        <v>316</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>317</v>
-      </c>
-      <c r="AK5" t="s">
-        <v>318</v>
-      </c>
-      <c r="AL5" t="s">
-        <v>319</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>320</v>
-      </c>
-      <c r="AN5" t="s">
-        <v>321</v>
-      </c>
-      <c r="AO5" t="s">
-        <v>322</v>
-      </c>
-      <c r="AP5" t="s">
-        <v>323</v>
-      </c>
-      <c r="AQ5" t="s">
-        <v>324</v>
-      </c>
-      <c r="AR5" t="s">
-        <v>325</v>
-      </c>
-      <c r="AS5" t="s">
-        <v>326</v>
-      </c>
-      <c r="AT5" t="s">
-        <v>327</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>328</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>329</v>
-      </c>
-      <c r="AW5" t="s">
-        <v>330</v>
-      </c>
-      <c r="AX5" t="s">
-        <v>331</v>
-      </c>
-      <c r="AY5" t="s">
-        <v>332</v>
-      </c>
-      <c r="AZ5" t="s">
-        <v>333</v>
-      </c>
-      <c r="BA5" t="s">
-        <v>334</v>
-      </c>
-      <c r="BB5" t="s">
-        <v>335</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>336</v>
-      </c>
-      <c r="BD5" t="s">
-        <v>337</v>
-      </c>
-      <c r="BE5" t="s">
-        <v>338</v>
-      </c>
-      <c r="BF5" t="s">
-        <v>339</v>
-      </c>
-      <c r="BG5" t="s">
-        <v>340</v>
-      </c>
-      <c r="BH5" t="s">
-        <v>341</v>
-      </c>
-      <c r="BI5" t="s">
-        <v>342</v>
-      </c>
-      <c r="BJ5" t="s">
-        <v>343</v>
-      </c>
-      <c r="BK5" t="s">
-        <v>344</v>
-      </c>
-      <c r="BL5" t="s">
-        <v>345</v>
-      </c>
-      <c r="BM5" t="s">
-        <v>346</v>
-      </c>
-      <c r="BN5" t="s">
-        <v>347</v>
-      </c>
-      <c r="BO5" t="s">
-        <v>348</v>
-      </c>
-      <c r="BP5" t="s">
-        <v>349</v>
-      </c>
-      <c r="BQ5" t="s">
-        <v>350</v>
-      </c>
-      <c r="BR5" t="s">
-        <v>351</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>352</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>353</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>354</v>
-      </c>
-      <c r="BW5" t="s">
-        <v>355</v>
-      </c>
-      <c r="CA5" t="s">
-        <v>356</v>
-      </c>
-      <c r="CB5" t="s">
-        <v>357</v>
-      </c>
-      <c r="CD5" t="s">
-        <v>358</v>
-      </c>
-      <c r="CE5" t="s">
-        <v>359</v>
-      </c>
-      <c r="CF5">
-        <v>1.8</v>
-      </c>
-      <c r="CG5">
-        <v>3.1</v>
-      </c>
-      <c r="CH5">
-        <v>4.75</v>
-      </c>
-      <c r="CJ5" t="s">
-        <v>360</v>
-      </c>
-      <c r="CK5" t="s">
-        <v>361</v>
-      </c>
-      <c r="CN5" t="s">
-        <v>362</v>
-      </c>
-      <c r="CO5" t="s">
-        <v>363</v>
-      </c>
-      <c r="CP5" t="s">
-        <v>364</v>
-      </c>
-      <c r="CQ5" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="6" spans="1:103" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>366</v>
-      </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -5091,255 +4333,201 @@
         <v>45089.583333333343</v>
       </c>
       <c r="G6" t="s">
+        <v>315</v>
+      </c>
+      <c r="H6" t="s">
+        <v>316</v>
+      </c>
+      <c r="I6" t="s">
+        <v>317</v>
+      </c>
+      <c r="J6" t="s">
+        <v>318</v>
+      </c>
+      <c r="K6" t="s">
+        <v>319</v>
+      </c>
+      <c r="L6" t="s">
+        <v>320</v>
+      </c>
+      <c r="M6" t="s">
+        <v>321</v>
+      </c>
+      <c r="N6" t="s">
+        <v>322</v>
+      </c>
+      <c r="O6" t="s">
+        <v>323</v>
+      </c>
+      <c r="P6" t="s">
+        <v>324</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>325</v>
+      </c>
+      <c r="R6" t="s">
+        <v>326</v>
+      </c>
+      <c r="S6" t="s">
+        <v>327</v>
+      </c>
+      <c r="T6" t="s">
+        <v>328</v>
+      </c>
+      <c r="U6" t="s">
+        <v>329</v>
+      </c>
+      <c r="V6" t="s">
+        <v>330</v>
+      </c>
+      <c r="W6" t="s">
+        <v>331</v>
+      </c>
+      <c r="X6" t="s">
+        <v>332</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>333</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>334</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>335</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>336</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>337</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>338</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>339</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>340</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>341</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>342</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>343</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>344</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>345</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>346</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>347</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>348</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>349</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>350</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>351</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>352</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>353</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>354</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>355</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>356</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>357</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>358</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>359</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>360</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>361</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>362</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>363</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>364</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>365</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>366</v>
+      </c>
+      <c r="BJ6">
+        <v>1.95</v>
+      </c>
+      <c r="BK6">
+        <v>3.2</v>
+      </c>
+      <c r="BL6">
+        <v>3.5</v>
+      </c>
+      <c r="BN6" t="s">
         <v>367</v>
       </c>
-      <c r="H6" t="s">
+      <c r="BO6" t="s">
         <v>368</v>
       </c>
-      <c r="I6" t="s">
-        <v>109</v>
-      </c>
-      <c r="J6" t="s">
-        <v>109</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="BP6" t="s">
         <v>369</v>
       </c>
-      <c r="L6" t="s">
+      <c r="BS6" t="s">
         <v>370</v>
       </c>
-      <c r="M6" s="3">
-        <v>64</v>
-      </c>
-      <c r="N6" s="3">
-        <v>36</v>
-      </c>
-      <c r="O6" t="s">
-        <v>117</v>
-      </c>
-      <c r="P6" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>116</v>
-      </c>
-      <c r="R6" t="s">
-        <v>114</v>
-      </c>
-      <c r="S6" t="s">
-        <v>109</v>
-      </c>
-      <c r="T6" t="s">
-        <v>116</v>
-      </c>
-      <c r="U6" t="s">
+      <c r="BV6" t="s">
+        <v>163</v>
+      </c>
+      <c r="BW6" t="s">
         <v>371</v>
       </c>
-      <c r="V6" t="s">
+    </row>
+    <row r="7" spans="1:81" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>372</v>
       </c>
-      <c r="AA6" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC6" t="s">
-        <v>373</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>374</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>375</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>376</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>377</v>
-      </c>
-      <c r="AH6" t="s">
-        <v>378</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>379</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>380</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>381</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>382</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>383</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>384</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>385</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>386</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>387</v>
-      </c>
-      <c r="AR6" t="s">
-        <v>388</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>389</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>390</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>391</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>392</v>
-      </c>
-      <c r="AW6" t="s">
-        <v>393</v>
-      </c>
-      <c r="AX6" t="s">
-        <v>394</v>
-      </c>
-      <c r="AY6" t="s">
-        <v>395</v>
-      </c>
-      <c r="AZ6" t="s">
-        <v>396</v>
-      </c>
-      <c r="BA6" t="s">
-        <v>397</v>
-      </c>
-      <c r="BB6" t="s">
-        <v>398</v>
-      </c>
-      <c r="BC6" t="s">
-        <v>399</v>
-      </c>
-      <c r="BD6" t="s">
-        <v>400</v>
-      </c>
-      <c r="BE6" t="s">
-        <v>401</v>
-      </c>
-      <c r="BF6" t="s">
-        <v>402</v>
-      </c>
-      <c r="BG6" t="s">
-        <v>403</v>
-      </c>
-      <c r="BH6" t="s">
-        <v>404</v>
-      </c>
-      <c r="BI6" t="s">
-        <v>405</v>
-      </c>
-      <c r="BJ6" t="s">
-        <v>406</v>
-      </c>
-      <c r="BK6" t="s">
-        <v>407</v>
-      </c>
-      <c r="BL6" t="s">
-        <v>408</v>
-      </c>
-      <c r="BM6" t="s">
-        <v>409</v>
-      </c>
-      <c r="BN6" t="s">
-        <v>410</v>
-      </c>
-      <c r="BO6" t="s">
-        <v>411</v>
-      </c>
-      <c r="BP6" t="s">
-        <v>412</v>
-      </c>
-      <c r="BQ6" t="s">
-        <v>413</v>
-      </c>
-      <c r="BR6" t="s">
-        <v>414</v>
-      </c>
-      <c r="BS6" t="s">
-        <v>415</v>
-      </c>
-      <c r="BT6" t="s">
-        <v>416</v>
-      </c>
-      <c r="BU6" t="s">
-        <v>417</v>
-      </c>
-      <c r="BV6" t="s">
-        <v>418</v>
-      </c>
-      <c r="BW6" t="s">
-        <v>419</v>
-      </c>
-      <c r="BX6" t="s">
-        <v>420</v>
-      </c>
-      <c r="BY6" t="s">
-        <v>421</v>
-      </c>
-      <c r="CA6" t="s">
-        <v>422</v>
-      </c>
-      <c r="CD6" t="s">
-        <v>423</v>
-      </c>
-      <c r="CE6" t="s">
-        <v>424</v>
-      </c>
-      <c r="CF6">
-        <v>1.95</v>
-      </c>
-      <c r="CG6">
-        <v>3.2</v>
-      </c>
-      <c r="CH6">
-        <v>3.5</v>
-      </c>
-      <c r="CJ6" t="s">
-        <v>425</v>
-      </c>
-      <c r="CK6" t="s">
-        <v>426</v>
-      </c>
-      <c r="CL6" t="s">
-        <v>427</v>
-      </c>
-      <c r="CO6" t="s">
-        <v>428</v>
-      </c>
-      <c r="CR6" t="s">
-        <v>204</v>
-      </c>
-      <c r="CS6" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="7" spans="1:103" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>430</v>
-      </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5348,246 +4536,192 @@
         <v>45087.895833333343</v>
       </c>
       <c r="G7" t="s">
-        <v>431</v>
+        <v>373</v>
       </c>
       <c r="H7" t="s">
-        <v>432</v>
+        <v>374</v>
       </c>
       <c r="I7" t="s">
-        <v>109</v>
+        <v>375</v>
       </c>
       <c r="J7" t="s">
-        <v>118</v>
+        <v>376</v>
       </c>
       <c r="K7" t="s">
-        <v>433</v>
+        <v>377</v>
       </c>
       <c r="L7" t="s">
-        <v>434</v>
-      </c>
-      <c r="M7" s="3">
-        <v>54</v>
-      </c>
-      <c r="N7" s="3">
-        <v>46</v>
+        <v>378</v>
+      </c>
+      <c r="M7" t="s">
+        <v>379</v>
+      </c>
+      <c r="N7" t="s">
+        <v>380</v>
       </c>
       <c r="O7" t="s">
-        <v>244</v>
+        <v>381</v>
       </c>
       <c r="P7" t="s">
-        <v>117</v>
+        <v>382</v>
       </c>
       <c r="Q7" t="s">
-        <v>241</v>
+        <v>383</v>
       </c>
       <c r="R7" t="s">
-        <v>114</v>
+        <v>384</v>
       </c>
       <c r="S7" t="s">
-        <v>118</v>
+        <v>385</v>
       </c>
       <c r="T7" t="s">
-        <v>116</v>
+        <v>386</v>
       </c>
       <c r="U7" t="s">
-        <v>435</v>
+        <v>387</v>
       </c>
       <c r="V7" t="s">
-        <v>112</v>
+        <v>388</v>
+      </c>
+      <c r="W7" t="s">
+        <v>389</v>
+      </c>
+      <c r="X7" t="s">
+        <v>390</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>391</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>392</v>
       </c>
       <c r="AA7" t="s">
-        <v>109</v>
+        <v>393</v>
       </c>
       <c r="AB7" t="s">
-        <v>109</v>
+        <v>394</v>
       </c>
       <c r="AC7" t="s">
-        <v>436</v>
+        <v>395</v>
       </c>
       <c r="AD7" t="s">
-        <v>437</v>
+        <v>396</v>
       </c>
       <c r="AE7" t="s">
-        <v>247</v>
+        <v>397</v>
       </c>
       <c r="AF7" t="s">
-        <v>438</v>
+        <v>398</v>
       </c>
       <c r="AG7" t="s">
-        <v>439</v>
+        <v>399</v>
       </c>
       <c r="AH7" t="s">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="AI7" t="s">
-        <v>441</v>
+        <v>401</v>
       </c>
       <c r="AJ7" t="s">
-        <v>442</v>
+        <v>402</v>
       </c>
       <c r="AK7" t="s">
-        <v>443</v>
+        <v>403</v>
       </c>
       <c r="AL7" t="s">
-        <v>444</v>
+        <v>404</v>
       </c>
       <c r="AM7" t="s">
-        <v>445</v>
-      </c>
-      <c r="AN7" t="s">
-        <v>446</v>
+        <v>405</v>
       </c>
       <c r="AO7" t="s">
-        <v>447</v>
+        <v>406</v>
       </c>
       <c r="AP7" t="s">
-        <v>448</v>
+        <v>407</v>
       </c>
       <c r="AQ7" t="s">
-        <v>449</v>
+        <v>408</v>
       </c>
       <c r="AR7" t="s">
-        <v>450</v>
+        <v>409</v>
       </c>
       <c r="AS7" t="s">
-        <v>451</v>
+        <v>410</v>
       </c>
       <c r="AT7" t="s">
-        <v>452</v>
+        <v>411</v>
       </c>
       <c r="AU7" t="s">
-        <v>453</v>
+        <v>412</v>
       </c>
       <c r="AV7" t="s">
-        <v>454</v>
+        <v>413</v>
       </c>
       <c r="AW7" t="s">
-        <v>455</v>
+        <v>414</v>
       </c>
       <c r="AX7" t="s">
-        <v>456</v>
+        <v>415</v>
       </c>
       <c r="AY7" t="s">
-        <v>457</v>
+        <v>416</v>
       </c>
       <c r="AZ7" t="s">
-        <v>458</v>
+        <v>417</v>
       </c>
       <c r="BA7" t="s">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="BB7" t="s">
-        <v>460</v>
+        <v>419</v>
       </c>
       <c r="BC7" t="s">
-        <v>461</v>
+        <v>420</v>
       </c>
       <c r="BD7" t="s">
-        <v>462</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>463</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>464</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>465</v>
+        <v>421</v>
       </c>
       <c r="BH7" t="s">
-        <v>466</v>
+        <v>422</v>
       </c>
       <c r="BI7" t="s">
-        <v>467</v>
-      </c>
-      <c r="BK7" t="s">
-        <v>468</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>469</v>
+        <v>423</v>
+      </c>
+      <c r="BJ7">
+        <v>1.4</v>
+      </c>
+      <c r="BK7">
+        <v>4</v>
+      </c>
+      <c r="BL7">
+        <v>6.5</v>
       </c>
       <c r="BM7" t="s">
-        <v>470</v>
+        <v>424</v>
       </c>
       <c r="BN7" t="s">
-        <v>471</v>
+        <v>425</v>
       </c>
       <c r="BO7" t="s">
-        <v>472</v>
+        <v>426</v>
       </c>
       <c r="BP7" t="s">
-        <v>473</v>
-      </c>
-      <c r="BQ7" t="s">
-        <v>474</v>
-      </c>
-      <c r="BR7" t="s">
-        <v>475</v>
-      </c>
-      <c r="BS7" t="s">
-        <v>476</v>
-      </c>
-      <c r="BT7" t="s">
-        <v>477</v>
-      </c>
-      <c r="BU7" t="s">
-        <v>478</v>
-      </c>
-      <c r="BV7" t="s">
-        <v>479</v>
-      </c>
-      <c r="BW7" t="s">
-        <v>480</v>
-      </c>
-      <c r="BX7" t="s">
-        <v>481</v>
-      </c>
-      <c r="BY7" t="s">
-        <v>482</v>
-      </c>
-      <c r="BZ7" t="s">
-        <v>483</v>
-      </c>
-      <c r="CD7" t="s">
-        <v>484</v>
-      </c>
-      <c r="CE7" t="s">
-        <v>485</v>
-      </c>
-      <c r="CF7">
-        <v>1.4</v>
-      </c>
-      <c r="CG7">
-        <v>4</v>
-      </c>
-      <c r="CH7">
-        <v>6.5</v>
-      </c>
-      <c r="CI7" t="s">
-        <v>486</v>
-      </c>
-      <c r="CJ7" t="s">
-        <v>487</v>
-      </c>
-      <c r="CK7" t="s">
-        <v>488</v>
-      </c>
-      <c r="CL7" t="s">
-        <v>489</v>
+        <v>427</v>
       </c>
     </row>
-    <row r="8" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>490</v>
+        <v>428</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5596,246 +4730,192 @@
         <v>45087.833333333343</v>
       </c>
       <c r="G8" t="s">
-        <v>491</v>
+        <v>429</v>
       </c>
       <c r="H8" t="s">
-        <v>492</v>
+        <v>430</v>
       </c>
       <c r="I8" t="s">
-        <v>109</v>
+        <v>431</v>
       </c>
       <c r="J8" t="s">
-        <v>109</v>
+        <v>432</v>
       </c>
       <c r="K8" t="s">
-        <v>493</v>
+        <v>433</v>
       </c>
       <c r="L8" t="s">
-        <v>494</v>
-      </c>
-      <c r="M8" s="3">
-        <v>71</v>
-      </c>
-      <c r="N8" s="3">
-        <v>29</v>
+        <v>434</v>
+      </c>
+      <c r="M8" t="s">
+        <v>435</v>
+      </c>
+      <c r="N8" t="s">
+        <v>436</v>
       </c>
       <c r="O8" t="s">
-        <v>372</v>
+        <v>437</v>
       </c>
       <c r="P8" t="s">
-        <v>179</v>
+        <v>438</v>
       </c>
       <c r="Q8" t="s">
-        <v>309</v>
+        <v>439</v>
       </c>
       <c r="R8" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="S8" t="s">
-        <v>114</v>
+        <v>440</v>
       </c>
       <c r="T8" t="s">
-        <v>241</v>
+        <v>441</v>
       </c>
       <c r="U8" t="s">
-        <v>244</v>
+        <v>442</v>
       </c>
       <c r="V8" t="s">
-        <v>113</v>
+        <v>443</v>
+      </c>
+      <c r="W8" t="s">
+        <v>444</v>
+      </c>
+      <c r="X8" t="s">
+        <v>445</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>446</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>447</v>
       </c>
       <c r="AA8" t="s">
-        <v>109</v>
+        <v>448</v>
       </c>
       <c r="AB8" t="s">
-        <v>114</v>
+        <v>449</v>
       </c>
       <c r="AC8" t="s">
-        <v>182</v>
+        <v>450</v>
       </c>
       <c r="AD8" t="s">
-        <v>495</v>
+        <v>451</v>
       </c>
       <c r="AE8" t="s">
-        <v>496</v>
+        <v>452</v>
       </c>
       <c r="AF8" t="s">
-        <v>497</v>
+        <v>453</v>
       </c>
       <c r="AG8" t="s">
-        <v>498</v>
+        <v>454</v>
       </c>
       <c r="AH8" t="s">
-        <v>499</v>
+        <v>455</v>
       </c>
       <c r="AI8" t="s">
-        <v>500</v>
+        <v>456</v>
       </c>
       <c r="AJ8" t="s">
-        <v>501</v>
+        <v>457</v>
       </c>
       <c r="AK8" t="s">
-        <v>502</v>
+        <v>458</v>
       </c>
       <c r="AL8" t="s">
-        <v>503</v>
+        <v>459</v>
       </c>
       <c r="AM8" t="s">
-        <v>504</v>
+        <v>460</v>
       </c>
       <c r="AN8" t="s">
-        <v>266</v>
+        <v>461</v>
       </c>
       <c r="AO8" t="s">
-        <v>505</v>
+        <v>462</v>
       </c>
       <c r="AP8" t="s">
-        <v>506</v>
+        <v>463</v>
       </c>
       <c r="AQ8" t="s">
-        <v>507</v>
+        <v>464</v>
       </c>
       <c r="AR8" t="s">
-        <v>508</v>
+        <v>465</v>
       </c>
       <c r="AS8" t="s">
-        <v>509</v>
+        <v>466</v>
       </c>
       <c r="AT8" t="s">
-        <v>510</v>
+        <v>467</v>
       </c>
       <c r="AU8" t="s">
-        <v>511</v>
+        <v>468</v>
       </c>
       <c r="AV8" t="s">
-        <v>512</v>
+        <v>469</v>
       </c>
       <c r="AW8" t="s">
-        <v>513</v>
+        <v>470</v>
       </c>
       <c r="AX8" t="s">
-        <v>514</v>
+        <v>471</v>
       </c>
       <c r="AY8" t="s">
-        <v>515</v>
+        <v>472</v>
       </c>
       <c r="AZ8" t="s">
-        <v>516</v>
+        <v>183</v>
       </c>
       <c r="BA8" t="s">
-        <v>517</v>
+        <v>473</v>
       </c>
       <c r="BB8" t="s">
-        <v>518</v>
+        <v>474</v>
       </c>
       <c r="BC8" t="s">
-        <v>519</v>
-      </c>
-      <c r="BD8" t="s">
-        <v>520</v>
+        <v>475</v>
       </c>
       <c r="BE8" t="s">
-        <v>521</v>
-      </c>
-      <c r="BF8" t="s">
-        <v>522</v>
-      </c>
-      <c r="BG8" t="s">
-        <v>523</v>
+        <v>476</v>
       </c>
       <c r="BH8" t="s">
-        <v>524</v>
+        <v>477</v>
       </c>
       <c r="BI8" t="s">
-        <v>525</v>
-      </c>
-      <c r="BJ8" t="s">
-        <v>526</v>
-      </c>
-      <c r="BK8" t="s">
-        <v>527</v>
-      </c>
-      <c r="BL8" t="s">
-        <v>528</v>
-      </c>
-      <c r="BM8" t="s">
-        <v>529</v>
+        <v>478</v>
+      </c>
+      <c r="BJ8">
+        <v>2</v>
+      </c>
+      <c r="BK8">
+        <v>3</v>
+      </c>
+      <c r="BL8">
+        <v>3.5</v>
       </c>
       <c r="BN8" t="s">
-        <v>530</v>
+        <v>479</v>
       </c>
       <c r="BO8" t="s">
-        <v>531</v>
-      </c>
-      <c r="BP8" t="s">
-        <v>532</v>
-      </c>
-      <c r="BQ8" t="s">
-        <v>533</v>
-      </c>
-      <c r="BR8" t="s">
-        <v>534</v>
+        <v>480</v>
       </c>
       <c r="BS8" t="s">
-        <v>535</v>
-      </c>
-      <c r="BT8" t="s">
-        <v>536</v>
-      </c>
-      <c r="BU8" t="s">
-        <v>537</v>
-      </c>
-      <c r="BV8" t="s">
-        <v>224</v>
-      </c>
-      <c r="BW8" t="s">
-        <v>538</v>
-      </c>
-      <c r="BX8" t="s">
-        <v>539</v>
-      </c>
-      <c r="BY8" t="s">
-        <v>540</v>
-      </c>
-      <c r="CA8" t="s">
-        <v>541</v>
-      </c>
-      <c r="CD8" t="s">
-        <v>542</v>
-      </c>
-      <c r="CE8" t="s">
-        <v>543</v>
-      </c>
-      <c r="CF8">
-        <v>2</v>
-      </c>
-      <c r="CG8">
-        <v>3</v>
-      </c>
-      <c r="CH8">
-        <v>3.5</v>
-      </c>
-      <c r="CJ8" t="s">
-        <v>544</v>
-      </c>
-      <c r="CK8" t="s">
-        <v>545</v>
-      </c>
-      <c r="CO8" t="s">
-        <v>546</v>
+        <v>481</v>
       </c>
     </row>
-    <row r="9" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>547</v>
+        <v>482</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5844,261 +4924,207 @@
         <v>45087.791666666657</v>
       </c>
       <c r="G9" t="s">
-        <v>548</v>
+        <v>483</v>
       </c>
       <c r="H9" t="s">
-        <v>549</v>
+        <v>484</v>
       </c>
       <c r="I9" t="s">
-        <v>109</v>
+        <v>485</v>
       </c>
       <c r="J9" t="s">
-        <v>118</v>
+        <v>486</v>
       </c>
       <c r="K9" t="s">
-        <v>550</v>
+        <v>487</v>
       </c>
       <c r="L9" t="s">
-        <v>551</v>
-      </c>
-      <c r="M9" s="3">
-        <v>33</v>
-      </c>
-      <c r="N9" s="3">
-        <v>67</v>
+        <v>488</v>
+      </c>
+      <c r="M9" t="s">
+        <v>489</v>
+      </c>
+      <c r="N9" t="s">
+        <v>490</v>
       </c>
       <c r="O9" t="s">
-        <v>244</v>
+        <v>491</v>
       </c>
       <c r="P9" t="s">
-        <v>117</v>
+        <v>492</v>
       </c>
       <c r="Q9" t="s">
-        <v>114</v>
+        <v>493</v>
       </c>
       <c r="R9" t="s">
-        <v>114</v>
+        <v>494</v>
       </c>
       <c r="S9" t="s">
-        <v>109</v>
+        <v>495</v>
       </c>
       <c r="T9" t="s">
-        <v>118</v>
+        <v>496</v>
       </c>
       <c r="U9" t="s">
-        <v>180</v>
+        <v>497</v>
       </c>
       <c r="V9" t="s">
-        <v>244</v>
+        <v>498</v>
+      </c>
+      <c r="W9" t="s">
+        <v>499</v>
+      </c>
+      <c r="X9" t="s">
+        <v>500</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>501</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>502</v>
       </c>
       <c r="AA9" t="s">
-        <v>109</v>
+        <v>503</v>
       </c>
       <c r="AB9" t="s">
-        <v>114</v>
+        <v>504</v>
       </c>
       <c r="AC9" t="s">
-        <v>552</v>
+        <v>505</v>
       </c>
       <c r="AD9" t="s">
-        <v>553</v>
+        <v>506</v>
       </c>
       <c r="AE9" t="s">
-        <v>121</v>
+        <v>507</v>
       </c>
       <c r="AF9" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="AG9" t="s">
-        <v>554</v>
+        <v>509</v>
       </c>
       <c r="AH9" t="s">
-        <v>555</v>
+        <v>510</v>
       </c>
       <c r="AI9" t="s">
-        <v>556</v>
+        <v>511</v>
       </c>
       <c r="AJ9" t="s">
-        <v>557</v>
+        <v>512</v>
       </c>
       <c r="AK9" t="s">
-        <v>558</v>
+        <v>513</v>
       </c>
       <c r="AL9" t="s">
-        <v>559</v>
+        <v>514</v>
       </c>
       <c r="AM9" t="s">
-        <v>560</v>
-      </c>
-      <c r="AN9" t="s">
-        <v>561</v>
+        <v>515</v>
       </c>
       <c r="AO9" t="s">
-        <v>562</v>
+        <v>516</v>
       </c>
       <c r="AP9" t="s">
-        <v>563</v>
+        <v>517</v>
       </c>
       <c r="AQ9" t="s">
-        <v>564</v>
+        <v>518</v>
       </c>
       <c r="AR9" t="s">
-        <v>565</v>
+        <v>519</v>
       </c>
       <c r="AS9" t="s">
-        <v>566</v>
+        <v>520</v>
       </c>
       <c r="AT9" t="s">
-        <v>567</v>
+        <v>521</v>
       </c>
       <c r="AU9" t="s">
-        <v>568</v>
+        <v>522</v>
       </c>
       <c r="AV9" t="s">
-        <v>569</v>
+        <v>523</v>
       </c>
       <c r="AW9" t="s">
-        <v>570</v>
+        <v>524</v>
       </c>
       <c r="AX9" t="s">
-        <v>571</v>
+        <v>525</v>
       </c>
       <c r="AY9" t="s">
-        <v>572</v>
+        <v>526</v>
       </c>
       <c r="AZ9" t="s">
-        <v>573</v>
+        <v>527</v>
       </c>
       <c r="BA9" t="s">
-        <v>574</v>
+        <v>528</v>
       </c>
       <c r="BB9" t="s">
-        <v>575</v>
+        <v>529</v>
       </c>
       <c r="BC9" t="s">
-        <v>576</v>
-      </c>
-      <c r="BD9" t="s">
-        <v>577</v>
+        <v>530</v>
       </c>
       <c r="BE9" t="s">
-        <v>578</v>
+        <v>531</v>
       </c>
       <c r="BF9" t="s">
-        <v>579</v>
+        <v>532</v>
       </c>
       <c r="BG9" t="s">
-        <v>580</v>
+        <v>533</v>
       </c>
       <c r="BH9" t="s">
-        <v>581</v>
+        <v>534</v>
       </c>
       <c r="BI9" t="s">
-        <v>582</v>
-      </c>
-      <c r="BK9" t="s">
-        <v>583</v>
-      </c>
-      <c r="BL9" t="s">
-        <v>584</v>
+        <v>535</v>
+      </c>
+      <c r="BJ9">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="BK9">
+        <v>2.88</v>
+      </c>
+      <c r="BL9">
+        <v>2.7</v>
       </c>
       <c r="BM9" t="s">
-        <v>585</v>
+        <v>536</v>
       </c>
       <c r="BN9" t="s">
-        <v>586</v>
+        <v>537</v>
       </c>
       <c r="BO9" t="s">
-        <v>587</v>
+        <v>538</v>
       </c>
       <c r="BP9" t="s">
-        <v>588</v>
-      </c>
-      <c r="BQ9" t="s">
-        <v>589</v>
-      </c>
-      <c r="BR9" t="s">
-        <v>590</v>
+        <v>539</v>
       </c>
       <c r="BS9" t="s">
-        <v>591</v>
-      </c>
-      <c r="BT9" t="s">
-        <v>592</v>
-      </c>
-      <c r="BU9" t="s">
-        <v>593</v>
+        <v>540</v>
       </c>
       <c r="BV9" t="s">
-        <v>594</v>
+        <v>541</v>
       </c>
       <c r="BW9" t="s">
-        <v>595</v>
-      </c>
-      <c r="BX9" t="s">
-        <v>596</v>
-      </c>
-      <c r="BY9" t="s">
-        <v>597</v>
-      </c>
-      <c r="CA9" t="s">
-        <v>598</v>
-      </c>
-      <c r="CB9" t="s">
-        <v>599</v>
-      </c>
-      <c r="CC9" t="s">
-        <v>600</v>
-      </c>
-      <c r="CD9" t="s">
-        <v>601</v>
-      </c>
-      <c r="CE9" t="s">
-        <v>602</v>
-      </c>
-      <c r="CF9">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="CG9">
-        <v>2.88</v>
-      </c>
-      <c r="CH9">
-        <v>2.7</v>
-      </c>
-      <c r="CI9" t="s">
-        <v>603</v>
-      </c>
-      <c r="CJ9" t="s">
-        <v>604</v>
-      </c>
-      <c r="CK9" t="s">
-        <v>605</v>
-      </c>
-      <c r="CL9" t="s">
-        <v>606</v>
-      </c>
-      <c r="CO9" t="s">
-        <v>607</v>
-      </c>
-      <c r="CR9" t="s">
-        <v>608</v>
-      </c>
-      <c r="CS9" t="s">
-        <v>609</v>
+        <v>542</v>
       </c>
     </row>
-    <row r="10" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>610</v>
+        <v>543</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6107,258 +5133,204 @@
         <v>45086.833333333343</v>
       </c>
       <c r="G10" t="s">
-        <v>611</v>
+        <v>544</v>
       </c>
       <c r="H10" t="s">
-        <v>612</v>
+        <v>545</v>
       </c>
       <c r="I10" t="s">
-        <v>114</v>
+        <v>546</v>
       </c>
       <c r="J10" t="s">
-        <v>118</v>
+        <v>547</v>
       </c>
       <c r="K10" t="s">
-        <v>613</v>
+        <v>548</v>
       </c>
       <c r="L10" t="s">
-        <v>614</v>
-      </c>
-      <c r="M10" s="3">
-        <v>55</v>
-      </c>
-      <c r="N10" s="3">
-        <v>45</v>
+        <v>549</v>
+      </c>
+      <c r="M10" t="s">
+        <v>550</v>
+      </c>
+      <c r="N10" t="s">
+        <v>551</v>
       </c>
       <c r="O10" t="s">
-        <v>112</v>
+        <v>552</v>
       </c>
       <c r="P10" t="s">
-        <v>116</v>
+        <v>553</v>
       </c>
       <c r="Q10" t="s">
-        <v>241</v>
+        <v>554</v>
       </c>
       <c r="R10" t="s">
-        <v>118</v>
+        <v>555</v>
       </c>
       <c r="S10" t="s">
-        <v>118</v>
+        <v>556</v>
       </c>
       <c r="T10" t="s">
-        <v>114</v>
+        <v>557</v>
       </c>
       <c r="U10" t="s">
-        <v>180</v>
+        <v>558</v>
       </c>
       <c r="V10" t="s">
-        <v>113</v>
+        <v>559</v>
+      </c>
+      <c r="W10" t="s">
+        <v>560</v>
+      </c>
+      <c r="X10" t="s">
+        <v>561</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>562</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>563</v>
       </c>
       <c r="AA10" t="s">
-        <v>118</v>
+        <v>564</v>
       </c>
       <c r="AB10" t="s">
-        <v>118</v>
+        <v>565</v>
       </c>
       <c r="AC10" t="s">
-        <v>615</v>
+        <v>566</v>
       </c>
       <c r="AD10" t="s">
-        <v>437</v>
+        <v>567</v>
       </c>
       <c r="AE10" t="s">
-        <v>616</v>
+        <v>568</v>
       </c>
       <c r="AF10" t="s">
-        <v>617</v>
+        <v>569</v>
       </c>
       <c r="AG10" t="s">
-        <v>618</v>
+        <v>570</v>
       </c>
       <c r="AH10" t="s">
-        <v>619</v>
+        <v>571</v>
       </c>
       <c r="AI10" t="s">
-        <v>620</v>
+        <v>572</v>
       </c>
       <c r="AJ10" t="s">
-        <v>621</v>
+        <v>573</v>
       </c>
       <c r="AK10" t="s">
-        <v>622</v>
+        <v>574</v>
       </c>
       <c r="AL10" t="s">
-        <v>623</v>
+        <v>575</v>
       </c>
       <c r="AM10" t="s">
-        <v>624</v>
+        <v>576</v>
       </c>
       <c r="AN10" t="s">
-        <v>625</v>
+        <v>577</v>
       </c>
       <c r="AO10" t="s">
-        <v>626</v>
+        <v>578</v>
       </c>
       <c r="AP10" t="s">
-        <v>627</v>
+        <v>579</v>
       </c>
       <c r="AQ10" t="s">
-        <v>628</v>
+        <v>580</v>
       </c>
       <c r="AR10" t="s">
-        <v>629</v>
+        <v>581</v>
       </c>
       <c r="AS10" t="s">
-        <v>630</v>
+        <v>582</v>
       </c>
       <c r="AT10" t="s">
-        <v>631</v>
+        <v>583</v>
       </c>
       <c r="AU10" t="s">
-        <v>632</v>
+        <v>584</v>
       </c>
       <c r="AV10" t="s">
-        <v>633</v>
+        <v>585</v>
       </c>
       <c r="AW10" t="s">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="AX10" t="s">
-        <v>635</v>
+        <v>587</v>
       </c>
       <c r="AY10" t="s">
-        <v>636</v>
+        <v>588</v>
       </c>
       <c r="AZ10" t="s">
-        <v>637</v>
+        <v>589</v>
       </c>
       <c r="BA10" t="s">
-        <v>638</v>
+        <v>590</v>
       </c>
       <c r="BB10" t="s">
-        <v>639</v>
+        <v>591</v>
       </c>
       <c r="BC10" t="s">
-        <v>640</v>
+        <v>592</v>
       </c>
       <c r="BD10" t="s">
-        <v>641</v>
+        <v>593</v>
       </c>
       <c r="BE10" t="s">
-        <v>642</v>
+        <v>594</v>
       </c>
       <c r="BF10" t="s">
-        <v>643</v>
+        <v>595</v>
       </c>
       <c r="BG10" t="s">
-        <v>644</v>
+        <v>596</v>
       </c>
       <c r="BH10" t="s">
-        <v>645</v>
+        <v>597</v>
       </c>
       <c r="BI10" t="s">
-        <v>646</v>
-      </c>
-      <c r="BJ10" t="s">
-        <v>647</v>
-      </c>
-      <c r="BK10" t="s">
-        <v>648</v>
-      </c>
-      <c r="BL10" t="s">
-        <v>649</v>
-      </c>
-      <c r="BM10" t="s">
-        <v>650</v>
+        <v>598</v>
+      </c>
+      <c r="BJ10">
+        <v>2.15</v>
+      </c>
+      <c r="BK10">
+        <v>3.2</v>
+      </c>
+      <c r="BL10">
+        <v>3.5</v>
       </c>
       <c r="BN10" t="s">
-        <v>651</v>
+        <v>599</v>
       </c>
       <c r="BO10" t="s">
-        <v>652</v>
+        <v>600</v>
       </c>
       <c r="BP10" t="s">
-        <v>653</v>
-      </c>
-      <c r="BQ10" t="s">
-        <v>654</v>
-      </c>
-      <c r="BR10" t="s">
-        <v>655</v>
-      </c>
-      <c r="BS10" t="s">
-        <v>656</v>
-      </c>
-      <c r="BT10" t="s">
-        <v>657</v>
-      </c>
-      <c r="BU10" t="s">
-        <v>658</v>
+        <v>601</v>
       </c>
       <c r="BV10" t="s">
-        <v>659</v>
-      </c>
-      <c r="BW10" t="s">
-        <v>660</v>
-      </c>
-      <c r="BX10" t="s">
-        <v>661</v>
-      </c>
-      <c r="BY10" t="s">
-        <v>662</v>
-      </c>
-      <c r="BZ10" t="s">
-        <v>663</v>
-      </c>
-      <c r="CA10" t="s">
-        <v>664</v>
-      </c>
-      <c r="CB10" t="s">
-        <v>665</v>
-      </c>
-      <c r="CC10" t="s">
-        <v>666</v>
-      </c>
-      <c r="CD10" t="s">
-        <v>667</v>
-      </c>
-      <c r="CE10" t="s">
-        <v>668</v>
-      </c>
-      <c r="CF10">
-        <v>2.15</v>
-      </c>
-      <c r="CG10">
-        <v>3.2</v>
-      </c>
-      <c r="CH10">
-        <v>3.5</v>
-      </c>
-      <c r="CJ10" t="s">
-        <v>669</v>
-      </c>
-      <c r="CK10" t="s">
-        <v>670</v>
-      </c>
-      <c r="CL10" t="s">
-        <v>671</v>
-      </c>
-      <c r="CR10" t="s">
-        <v>672</v>
+        <v>602</v>
       </c>
     </row>
-    <row r="11" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>673</v>
+        <v>603</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6367,252 +5339,198 @@
         <v>45086.645833333343</v>
       </c>
       <c r="G11" t="s">
-        <v>674</v>
+        <v>604</v>
       </c>
       <c r="H11" t="s">
-        <v>675</v>
+        <v>605</v>
       </c>
       <c r="I11" t="s">
-        <v>118</v>
+        <v>606</v>
       </c>
       <c r="J11" t="s">
-        <v>118</v>
+        <v>607</v>
       </c>
       <c r="K11" t="s">
-        <v>676</v>
+        <v>608</v>
       </c>
       <c r="L11" t="s">
-        <v>677</v>
-      </c>
-      <c r="M11" s="3">
-        <v>49</v>
-      </c>
-      <c r="N11" s="3">
-        <v>51</v>
+        <v>609</v>
+      </c>
+      <c r="M11" t="s">
+        <v>610</v>
+      </c>
+      <c r="N11" t="s">
+        <v>611</v>
       </c>
       <c r="O11" t="s">
-        <v>115</v>
+        <v>612</v>
       </c>
       <c r="P11" t="s">
-        <v>115</v>
+        <v>613</v>
       </c>
       <c r="Q11" t="s">
-        <v>114</v>
+        <v>614</v>
       </c>
       <c r="R11" t="s">
-        <v>114</v>
+        <v>615</v>
       </c>
       <c r="S11" t="s">
-        <v>109</v>
+        <v>616</v>
       </c>
       <c r="T11" t="s">
-        <v>241</v>
+        <v>617</v>
       </c>
       <c r="U11" t="s">
-        <v>180</v>
+        <v>618</v>
       </c>
       <c r="V11" t="s">
-        <v>435</v>
+        <v>619</v>
+      </c>
+      <c r="W11" t="s">
+        <v>620</v>
+      </c>
+      <c r="X11" t="s">
+        <v>621</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>622</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>162</v>
       </c>
       <c r="AA11" t="s">
-        <v>118</v>
+        <v>623</v>
       </c>
       <c r="AB11" t="s">
-        <v>114</v>
+        <v>624</v>
       </c>
       <c r="AC11" t="s">
-        <v>678</v>
+        <v>625</v>
       </c>
       <c r="AD11" t="s">
-        <v>679</v>
+        <v>626</v>
       </c>
       <c r="AE11" t="s">
-        <v>680</v>
+        <v>627</v>
       </c>
       <c r="AF11" t="s">
-        <v>375</v>
+        <v>628</v>
       </c>
       <c r="AG11" t="s">
-        <v>681</v>
+        <v>629</v>
       </c>
       <c r="AH11" t="s">
-        <v>682</v>
+        <v>630</v>
       </c>
       <c r="AI11" t="s">
-        <v>683</v>
+        <v>631</v>
       </c>
       <c r="AJ11" t="s">
-        <v>684</v>
+        <v>632</v>
       </c>
       <c r="AK11" t="s">
-        <v>685</v>
+        <v>633</v>
       </c>
       <c r="AL11" t="s">
-        <v>686</v>
+        <v>634</v>
       </c>
       <c r="AM11" t="s">
-        <v>687</v>
+        <v>635</v>
       </c>
       <c r="AN11" t="s">
-        <v>688</v>
+        <v>636</v>
       </c>
       <c r="AO11" t="s">
-        <v>689</v>
+        <v>637</v>
       </c>
       <c r="AP11" t="s">
-        <v>690</v>
+        <v>638</v>
       </c>
       <c r="AQ11" t="s">
-        <v>691</v>
+        <v>639</v>
       </c>
       <c r="AR11" t="s">
-        <v>692</v>
+        <v>640</v>
       </c>
       <c r="AS11" t="s">
-        <v>693</v>
+        <v>641</v>
       </c>
       <c r="AT11" t="s">
-        <v>694</v>
+        <v>642</v>
       </c>
       <c r="AU11" t="s">
-        <v>695</v>
+        <v>643</v>
       </c>
       <c r="AV11" t="s">
-        <v>203</v>
+        <v>644</v>
       </c>
       <c r="AW11" t="s">
-        <v>696</v>
+        <v>645</v>
       </c>
       <c r="AX11" t="s">
-        <v>697</v>
-      </c>
-      <c r="AY11" t="s">
-        <v>698</v>
+        <v>646</v>
       </c>
       <c r="AZ11" t="s">
-        <v>699</v>
+        <v>647</v>
       </c>
       <c r="BA11" t="s">
-        <v>700</v>
+        <v>648</v>
       </c>
       <c r="BB11" t="s">
-        <v>701</v>
-      </c>
-      <c r="BC11" t="s">
-        <v>702</v>
-      </c>
-      <c r="BD11" t="s">
-        <v>703</v>
+        <v>649</v>
       </c>
       <c r="BE11" t="s">
-        <v>704</v>
+        <v>650</v>
       </c>
       <c r="BF11" t="s">
-        <v>705</v>
+        <v>651</v>
       </c>
       <c r="BG11" t="s">
-        <v>706</v>
+        <v>652</v>
       </c>
       <c r="BH11" t="s">
-        <v>707</v>
+        <v>653</v>
       </c>
       <c r="BI11" t="s">
-        <v>708</v>
-      </c>
-      <c r="BJ11" t="s">
-        <v>709</v>
-      </c>
-      <c r="BK11" t="s">
-        <v>710</v>
-      </c>
-      <c r="BL11" t="s">
-        <v>711</v>
-      </c>
-      <c r="BM11" t="s">
-        <v>712</v>
+        <v>654</v>
+      </c>
+      <c r="BJ11">
+        <v>2.8</v>
+      </c>
+      <c r="BK11">
+        <v>3.1</v>
+      </c>
+      <c r="BL11">
+        <v>2.4</v>
       </c>
       <c r="BN11" t="s">
-        <v>713</v>
+        <v>655</v>
       </c>
       <c r="BO11" t="s">
-        <v>714</v>
-      </c>
-      <c r="BP11" t="s">
-        <v>715</v>
-      </c>
-      <c r="BQ11" t="s">
-        <v>716</v>
+        <v>656</v>
       </c>
       <c r="BR11" t="s">
-        <v>717</v>
+        <v>657</v>
       </c>
       <c r="BS11" t="s">
-        <v>718</v>
+        <v>658</v>
       </c>
       <c r="BT11" t="s">
-        <v>719</v>
-      </c>
-      <c r="BV11" t="s">
-        <v>720</v>
-      </c>
-      <c r="BW11" t="s">
-        <v>721</v>
-      </c>
-      <c r="BX11" t="s">
-        <v>722</v>
-      </c>
-      <c r="CA11" t="s">
-        <v>723</v>
-      </c>
-      <c r="CB11" t="s">
-        <v>724</v>
-      </c>
-      <c r="CC11" t="s">
-        <v>725</v>
-      </c>
-      <c r="CD11" t="s">
-        <v>726</v>
-      </c>
-      <c r="CE11" t="s">
-        <v>727</v>
-      </c>
-      <c r="CF11">
-        <v>2.8</v>
-      </c>
-      <c r="CG11">
-        <v>3.1</v>
-      </c>
-      <c r="CH11">
-        <v>2.4</v>
-      </c>
-      <c r="CJ11" t="s">
-        <v>728</v>
-      </c>
-      <c r="CK11" t="s">
-        <v>729</v>
-      </c>
-      <c r="CN11" t="s">
-        <v>730</v>
-      </c>
-      <c r="CO11" t="s">
-        <v>731</v>
-      </c>
-      <c r="CP11" t="s">
-        <v>732</v>
+        <v>659</v>
       </c>
     </row>
-    <row r="12" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>733</v>
+        <v>660</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6621,261 +5539,195 @@
         <v>45081.895833333343</v>
       </c>
       <c r="G12" t="s">
-        <v>492</v>
+        <v>430</v>
       </c>
       <c r="H12" t="s">
-        <v>734</v>
+        <v>661</v>
       </c>
       <c r="I12" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="J12" t="s">
-        <v>109</v>
+        <v>662</v>
       </c>
       <c r="K12" t="s">
-        <v>110</v>
+        <v>443</v>
       </c>
       <c r="L12" t="s">
-        <v>735</v>
-      </c>
-      <c r="M12" s="3">
-        <v>45</v>
-      </c>
-      <c r="N12" s="3">
-        <v>55</v>
+        <v>444</v>
+      </c>
+      <c r="M12" t="s">
+        <v>445</v>
+      </c>
+      <c r="N12" t="s">
+        <v>446</v>
       </c>
       <c r="O12" t="s">
-        <v>736</v>
+        <v>481</v>
       </c>
       <c r="P12" t="s">
-        <v>244</v>
+        <v>448</v>
       </c>
       <c r="Q12" t="s">
-        <v>244</v>
+        <v>449</v>
       </c>
       <c r="R12" t="s">
-        <v>309</v>
+        <v>450</v>
       </c>
       <c r="S12" t="s">
-        <v>109</v>
+        <v>453</v>
       </c>
       <c r="T12" t="s">
-        <v>109</v>
+        <v>452</v>
       </c>
       <c r="U12" t="s">
-        <v>117</v>
+        <v>451</v>
       </c>
       <c r="V12" t="s">
-        <v>179</v>
+        <v>663</v>
       </c>
       <c r="W12" t="s">
-        <v>737</v>
+        <v>664</v>
       </c>
       <c r="X12" t="s">
-        <v>738</v>
+        <v>665</v>
       </c>
       <c r="Y12" t="s">
-        <v>739</v>
+        <v>666</v>
       </c>
       <c r="Z12" t="s">
-        <v>740</v>
+        <v>667</v>
       </c>
       <c r="AA12" t="s">
-        <v>118</v>
+        <v>668</v>
       </c>
       <c r="AB12" t="s">
-        <v>109</v>
+        <v>669</v>
       </c>
       <c r="AC12" t="s">
-        <v>741</v>
+        <v>670</v>
       </c>
       <c r="AD12" t="s">
-        <v>742</v>
+        <v>671</v>
       </c>
       <c r="AE12" t="s">
-        <v>743</v>
+        <v>672</v>
       </c>
       <c r="AF12" t="s">
-        <v>744</v>
+        <v>673</v>
       </c>
       <c r="AG12" t="s">
-        <v>508</v>
+        <v>462</v>
       </c>
       <c r="AH12" t="s">
-        <v>509</v>
+        <v>674</v>
       </c>
       <c r="AI12" t="s">
-        <v>510</v>
+        <v>675</v>
       </c>
       <c r="AJ12" t="s">
-        <v>511</v>
+        <v>464</v>
       </c>
       <c r="AK12" t="s">
-        <v>546</v>
+        <v>465</v>
       </c>
       <c r="AL12" t="s">
-        <v>513</v>
+        <v>466</v>
       </c>
       <c r="AM12" t="s">
-        <v>514</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>515</v>
+        <v>467</v>
       </c>
       <c r="AO12" t="s">
-        <v>518</v>
+        <v>676</v>
       </c>
       <c r="AP12" t="s">
-        <v>517</v>
+        <v>677</v>
       </c>
       <c r="AQ12" t="s">
-        <v>516</v>
+        <v>678</v>
       </c>
       <c r="AR12" t="s">
-        <v>745</v>
+        <v>679</v>
       </c>
       <c r="AS12" t="s">
-        <v>746</v>
+        <v>680</v>
       </c>
       <c r="AT12" t="s">
-        <v>747</v>
+        <v>681</v>
       </c>
       <c r="AU12" t="s">
-        <v>748</v>
+        <v>682</v>
       </c>
       <c r="AV12" t="s">
-        <v>749</v>
+        <v>473</v>
       </c>
       <c r="AW12" t="s">
-        <v>750</v>
+        <v>183</v>
       </c>
       <c r="AX12" t="s">
-        <v>751</v>
+        <v>475</v>
       </c>
       <c r="AY12" t="s">
-        <v>752</v>
+        <v>447</v>
       </c>
       <c r="AZ12" t="s">
-        <v>753</v>
+        <v>683</v>
       </c>
       <c r="BA12" t="s">
-        <v>754</v>
+        <v>684</v>
       </c>
       <c r="BB12" t="s">
-        <v>755</v>
+        <v>685</v>
       </c>
       <c r="BC12" t="s">
-        <v>527</v>
-      </c>
-      <c r="BD12" t="s">
-        <v>756</v>
+        <v>686</v>
       </c>
       <c r="BE12" t="s">
-        <v>757</v>
+        <v>687</v>
       </c>
       <c r="BF12" t="s">
-        <v>529</v>
-      </c>
-      <c r="BG12" t="s">
-        <v>530</v>
+        <v>688</v>
       </c>
       <c r="BH12" t="s">
-        <v>531</v>
+        <v>478</v>
       </c>
       <c r="BI12" t="s">
-        <v>532</v>
-      </c>
-      <c r="BK12" t="s">
-        <v>758</v>
-      </c>
-      <c r="BL12" t="s">
-        <v>759</v>
+        <v>689</v>
+      </c>
+      <c r="BJ12">
+        <v>1.95</v>
+      </c>
+      <c r="BK12">
+        <v>3.2</v>
+      </c>
+      <c r="BL12">
+        <v>4.2</v>
       </c>
       <c r="BM12" t="s">
-        <v>760</v>
+        <v>468</v>
       </c>
       <c r="BN12" t="s">
-        <v>761</v>
+        <v>474</v>
       </c>
       <c r="BO12" t="s">
-        <v>762</v>
-      </c>
-      <c r="BP12" t="s">
-        <v>763</v>
-      </c>
-      <c r="BQ12" t="s">
-        <v>764</v>
-      </c>
-      <c r="BR12" t="s">
-        <v>538</v>
+        <v>476</v>
       </c>
       <c r="BS12" t="s">
-        <v>224</v>
-      </c>
-      <c r="BT12" t="s">
-        <v>540</v>
-      </c>
-      <c r="BU12" t="s">
-        <v>512</v>
-      </c>
-      <c r="BV12" t="s">
-        <v>765</v>
-      </c>
-      <c r="BW12" t="s">
-        <v>766</v>
-      </c>
-      <c r="BX12" t="s">
-        <v>767</v>
-      </c>
-      <c r="BY12" t="s">
-        <v>768</v>
-      </c>
-      <c r="CA12" t="s">
-        <v>769</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>770</v>
-      </c>
-      <c r="CD12" t="s">
-        <v>543</v>
-      </c>
-      <c r="CE12" t="s">
-        <v>771</v>
-      </c>
-      <c r="CF12">
-        <v>1.95</v>
-      </c>
-      <c r="CG12">
-        <v>3.2</v>
-      </c>
-      <c r="CH12">
-        <v>4.2</v>
-      </c>
-      <c r="CI12" t="s">
-        <v>533</v>
-      </c>
-      <c r="CJ12" t="s">
-        <v>539</v>
-      </c>
-      <c r="CK12" t="s">
-        <v>541</v>
-      </c>
-      <c r="CO12" t="s">
-        <v>772</v>
+        <v>690</v>
       </c>
     </row>
-    <row r="13" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>773</v>
+        <v>691</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6884,276 +5736,210 @@
         <v>45081.708333333343</v>
       </c>
       <c r="G13" t="s">
-        <v>774</v>
+        <v>692</v>
       </c>
       <c r="H13" t="s">
-        <v>611</v>
+        <v>544</v>
       </c>
       <c r="I13" t="s">
-        <v>114</v>
+        <v>485</v>
       </c>
       <c r="J13" t="s">
-        <v>109</v>
+        <v>693</v>
       </c>
       <c r="K13" t="s">
+        <v>694</v>
+      </c>
+      <c r="L13" t="s">
+        <v>695</v>
+      </c>
+      <c r="M13" t="s">
+        <v>696</v>
+      </c>
+      <c r="N13" t="s">
+        <v>697</v>
+      </c>
+      <c r="O13" t="s">
+        <v>698</v>
+      </c>
+      <c r="P13" t="s">
+        <v>699</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>700</v>
+      </c>
+      <c r="R13" t="s">
+        <v>701</v>
+      </c>
+      <c r="S13" t="s">
+        <v>702</v>
+      </c>
+      <c r="T13" t="s">
+        <v>703</v>
+      </c>
+      <c r="U13" t="s">
+        <v>704</v>
+      </c>
+      <c r="V13" t="s">
+        <v>548</v>
+      </c>
+      <c r="W13" t="s">
+        <v>587</v>
+      </c>
+      <c r="X13" t="s">
+        <v>705</v>
+      </c>
+      <c r="Y13" t="s">
         <v>550</v>
       </c>
-      <c r="L13" t="s">
-        <v>775</v>
-      </c>
-      <c r="M13" s="3">
-        <v>45</v>
-      </c>
-      <c r="N13" s="3">
-        <v>55</v>
-      </c>
-      <c r="O13" t="s">
-        <v>180</v>
-      </c>
-      <c r="P13" t="s">
-        <v>372</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>179</v>
-      </c>
-      <c r="R13" t="s">
-        <v>435</v>
-      </c>
-      <c r="S13" t="s">
-        <v>116</v>
-      </c>
-      <c r="T13" t="s">
-        <v>114</v>
-      </c>
-      <c r="U13" t="s">
-        <v>113</v>
-      </c>
-      <c r="V13" t="s">
-        <v>117</v>
-      </c>
-      <c r="W13" t="s">
-        <v>776</v>
-      </c>
-      <c r="X13" t="s">
-        <v>777</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>183</v>
-      </c>
       <c r="Z13" t="s">
-        <v>778</v>
+        <v>552</v>
       </c>
       <c r="AA13" t="s">
-        <v>109</v>
+        <v>585</v>
       </c>
       <c r="AB13" t="s">
-        <v>114</v>
+        <v>555</v>
       </c>
       <c r="AC13" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="AD13" t="s">
-        <v>779</v>
+        <v>553</v>
       </c>
       <c r="AE13" t="s">
-        <v>780</v>
+        <v>557</v>
       </c>
       <c r="AF13" t="s">
-        <v>781</v>
+        <v>558</v>
       </c>
       <c r="AG13" t="s">
-        <v>782</v>
+        <v>706</v>
       </c>
       <c r="AH13" t="s">
-        <v>783</v>
+        <v>707</v>
       </c>
       <c r="AI13" t="s">
-        <v>784</v>
+        <v>708</v>
       </c>
       <c r="AJ13" t="s">
-        <v>785</v>
+        <v>709</v>
       </c>
       <c r="AK13" t="s">
-        <v>786</v>
+        <v>710</v>
       </c>
       <c r="AL13" t="s">
-        <v>787</v>
+        <v>711</v>
       </c>
       <c r="AM13" t="s">
-        <v>788</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>789</v>
+        <v>712</v>
       </c>
       <c r="AO13" t="s">
-        <v>790</v>
+        <v>586</v>
       </c>
       <c r="AP13" t="s">
-        <v>791</v>
+        <v>713</v>
       </c>
       <c r="AQ13" t="s">
-        <v>792</v>
+        <v>551</v>
       </c>
       <c r="AR13" t="s">
-        <v>618</v>
+        <v>573</v>
       </c>
       <c r="AS13" t="s">
-        <v>657</v>
+        <v>575</v>
       </c>
       <c r="AT13" t="s">
-        <v>793</v>
+        <v>576</v>
       </c>
       <c r="AU13" t="s">
-        <v>620</v>
+        <v>577</v>
       </c>
       <c r="AV13" t="s">
-        <v>622</v>
+        <v>714</v>
       </c>
       <c r="AW13" t="s">
-        <v>655</v>
+        <v>715</v>
       </c>
       <c r="AX13" t="s">
-        <v>625</v>
+        <v>716</v>
       </c>
       <c r="AY13" t="s">
-        <v>626</v>
+        <v>717</v>
       </c>
       <c r="AZ13" t="s">
-        <v>623</v>
+        <v>572</v>
       </c>
       <c r="BA13" t="s">
-        <v>627</v>
+        <v>570</v>
       </c>
       <c r="BB13" t="s">
-        <v>628</v>
+        <v>574</v>
       </c>
       <c r="BC13" t="s">
-        <v>794</v>
+        <v>549</v>
       </c>
       <c r="BD13" t="s">
-        <v>795</v>
+        <v>571</v>
       </c>
       <c r="BE13" t="s">
-        <v>796</v>
+        <v>599</v>
       </c>
       <c r="BF13" t="s">
-        <v>797</v>
+        <v>554</v>
       </c>
       <c r="BG13" t="s">
-        <v>798</v>
+        <v>600</v>
       </c>
       <c r="BH13" t="s">
-        <v>799</v>
+        <v>718</v>
       </c>
       <c r="BI13" t="s">
-        <v>800</v>
-      </c>
-      <c r="BK13" t="s">
-        <v>656</v>
-      </c>
-      <c r="BL13" t="s">
-        <v>801</v>
+        <v>597</v>
+      </c>
+      <c r="BJ13">
+        <v>2.25</v>
+      </c>
+      <c r="BK13">
+        <v>3.1</v>
+      </c>
+      <c r="BL13">
+        <v>3.3</v>
       </c>
       <c r="BM13" t="s">
-        <v>621</v>
+        <v>719</v>
       </c>
       <c r="BN13" t="s">
-        <v>643</v>
+        <v>720</v>
       </c>
       <c r="BO13" t="s">
-        <v>645</v>
-      </c>
-      <c r="BP13" t="s">
-        <v>646</v>
+        <v>721</v>
       </c>
       <c r="BQ13" t="s">
-        <v>647</v>
-      </c>
-      <c r="BR13" t="s">
-        <v>802</v>
-      </c>
-      <c r="BS13" t="s">
-        <v>803</v>
-      </c>
-      <c r="BT13" t="s">
-        <v>804</v>
-      </c>
-      <c r="BU13" t="s">
-        <v>805</v>
-      </c>
-      <c r="BV13" t="s">
-        <v>642</v>
-      </c>
-      <c r="BW13" t="s">
-        <v>640</v>
+        <v>588</v>
       </c>
       <c r="BX13" t="s">
-        <v>644</v>
+        <v>601</v>
       </c>
       <c r="BY13" t="s">
-        <v>619</v>
+        <v>722</v>
       </c>
       <c r="BZ13" t="s">
-        <v>641</v>
-      </c>
-      <c r="CA13" t="s">
-        <v>669</v>
-      </c>
-      <c r="CB13" t="s">
-        <v>624</v>
-      </c>
-      <c r="CC13" t="s">
-        <v>670</v>
-      </c>
-      <c r="CD13" t="s">
-        <v>806</v>
-      </c>
-      <c r="CE13" t="s">
-        <v>667</v>
-      </c>
-      <c r="CF13">
-        <v>2.25</v>
-      </c>
-      <c r="CG13">
-        <v>3.1</v>
-      </c>
-      <c r="CH13">
-        <v>3.3</v>
-      </c>
-      <c r="CI13" t="s">
-        <v>807</v>
-      </c>
-      <c r="CJ13" t="s">
-        <v>808</v>
-      </c>
-      <c r="CK13" t="s">
-        <v>809</v>
-      </c>
-      <c r="CM13" t="s">
-        <v>658</v>
-      </c>
-      <c r="CT13" t="s">
-        <v>671</v>
-      </c>
-      <c r="CU13" t="s">
-        <v>810</v>
-      </c>
-      <c r="CV13" t="s">
-        <v>672</v>
+        <v>602</v>
       </c>
     </row>
-    <row r="14" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>811</v>
+        <v>723</v>
       </c>
       <c r="B14" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -7162,261 +5948,195 @@
         <v>45081.583333333343</v>
       </c>
       <c r="G14" t="s">
-        <v>304</v>
+        <v>258</v>
       </c>
       <c r="H14" t="s">
-        <v>812</v>
+        <v>724</v>
       </c>
       <c r="I14" t="s">
-        <v>118</v>
+        <v>725</v>
       </c>
       <c r="J14" t="s">
-        <v>118</v>
+        <v>261</v>
       </c>
       <c r="K14" t="s">
-        <v>813</v>
+        <v>262</v>
       </c>
       <c r="L14" t="s">
-        <v>307</v>
-      </c>
-      <c r="M14" s="3">
-        <v>52</v>
-      </c>
-      <c r="N14" s="3">
-        <v>48</v>
+        <v>263</v>
+      </c>
+      <c r="M14" t="s">
+        <v>264</v>
+      </c>
+      <c r="N14" t="s">
+        <v>285</v>
       </c>
       <c r="O14" t="s">
-        <v>180</v>
+        <v>269</v>
       </c>
       <c r="P14" t="s">
-        <v>179</v>
+        <v>268</v>
       </c>
       <c r="Q14" t="s">
-        <v>114</v>
+        <v>266</v>
       </c>
       <c r="R14" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="S14" t="s">
-        <v>116</v>
+        <v>309</v>
       </c>
       <c r="T14" t="s">
-        <v>114</v>
+        <v>271</v>
       </c>
       <c r="U14" t="s">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="V14" t="s">
-        <v>244</v>
+        <v>726</v>
       </c>
       <c r="W14" t="s">
-        <v>814</v>
+        <v>727</v>
       </c>
       <c r="X14" t="s">
-        <v>815</v>
+        <v>728</v>
       </c>
       <c r="Y14" t="s">
-        <v>816</v>
+        <v>729</v>
       </c>
       <c r="Z14" t="s">
-        <v>817</v>
+        <v>730</v>
       </c>
       <c r="AA14" t="s">
-        <v>109</v>
+        <v>731</v>
       </c>
       <c r="AB14" t="s">
-        <v>109</v>
+        <v>732</v>
       </c>
       <c r="AC14" t="s">
-        <v>311</v>
+        <v>733</v>
       </c>
       <c r="AD14" t="s">
-        <v>818</v>
+        <v>734</v>
       </c>
       <c r="AE14" t="s">
-        <v>819</v>
+        <v>735</v>
       </c>
       <c r="AF14" t="s">
-        <v>820</v>
+        <v>736</v>
       </c>
       <c r="AG14" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="AH14" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="AI14" t="s">
-        <v>316</v>
+        <v>286</v>
       </c>
       <c r="AJ14" t="s">
-        <v>337</v>
+        <v>265</v>
       </c>
       <c r="AK14" t="s">
-        <v>321</v>
+        <v>287</v>
       </c>
       <c r="AL14" t="s">
-        <v>320</v>
+        <v>737</v>
       </c>
       <c r="AM14" t="s">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="AN14" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="AO14" t="s">
-        <v>361</v>
+        <v>738</v>
       </c>
       <c r="AP14" t="s">
-        <v>323</v>
+        <v>739</v>
       </c>
       <c r="AQ14" t="s">
-        <v>322</v>
+        <v>740</v>
       </c>
       <c r="AR14" t="s">
-        <v>821</v>
+        <v>741</v>
       </c>
       <c r="AS14" t="s">
-        <v>822</v>
+        <v>742</v>
       </c>
       <c r="AT14" t="s">
-        <v>823</v>
+        <v>743</v>
       </c>
       <c r="AU14" t="s">
-        <v>824</v>
+        <v>744</v>
       </c>
       <c r="AV14" t="s">
-        <v>825</v>
+        <v>289</v>
       </c>
       <c r="AW14" t="s">
-        <v>826</v>
+        <v>291</v>
       </c>
       <c r="AX14" t="s">
-        <v>827</v>
+        <v>299</v>
       </c>
       <c r="AY14" t="s">
-        <v>828</v>
+        <v>300</v>
       </c>
       <c r="AZ14" t="s">
-        <v>829</v>
+        <v>745</v>
       </c>
       <c r="BA14" t="s">
-        <v>830</v>
+        <v>746</v>
       </c>
       <c r="BB14" t="s">
-        <v>831</v>
-      </c>
-      <c r="BC14" t="s">
-        <v>336</v>
-      </c>
-      <c r="BD14" t="s">
-        <v>353</v>
+        <v>747</v>
       </c>
       <c r="BE14" t="s">
-        <v>338</v>
+        <v>748</v>
       </c>
       <c r="BF14" t="s">
-        <v>317</v>
+        <v>749</v>
       </c>
       <c r="BG14" t="s">
-        <v>339</v>
+        <v>750</v>
       </c>
       <c r="BH14" t="s">
-        <v>832</v>
+        <v>306</v>
       </c>
       <c r="BI14" t="s">
-        <v>342</v>
-      </c>
-      <c r="BJ14" t="s">
-        <v>362</v>
-      </c>
-      <c r="BK14" t="s">
-        <v>833</v>
-      </c>
-      <c r="BL14" t="s">
-        <v>834</v>
-      </c>
-      <c r="BM14" t="s">
-        <v>835</v>
+        <v>751</v>
+      </c>
+      <c r="BJ14">
+        <v>1.91</v>
+      </c>
+      <c r="BK14">
+        <v>3.25</v>
+      </c>
+      <c r="BL14">
+        <v>4.33</v>
       </c>
       <c r="BN14" t="s">
-        <v>836</v>
-      </c>
-      <c r="BO14" t="s">
-        <v>837</v>
-      </c>
-      <c r="BP14" t="s">
-        <v>838</v>
+        <v>308</v>
       </c>
       <c r="BQ14" t="s">
-        <v>839</v>
-      </c>
-      <c r="BR14" t="s">
-        <v>341</v>
+        <v>752</v>
       </c>
       <c r="BS14" t="s">
-        <v>343</v>
-      </c>
-      <c r="BT14" t="s">
-        <v>351</v>
-      </c>
-      <c r="BU14" t="s">
-        <v>352</v>
-      </c>
-      <c r="BV14" t="s">
-        <v>840</v>
-      </c>
-      <c r="BW14" t="s">
-        <v>841</v>
-      </c>
-      <c r="BX14" t="s">
-        <v>842</v>
-      </c>
-      <c r="CA14" t="s">
-        <v>843</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>844</v>
-      </c>
-      <c r="CC14" t="s">
-        <v>845</v>
-      </c>
-      <c r="CD14" t="s">
-        <v>358</v>
-      </c>
-      <c r="CE14" t="s">
-        <v>846</v>
-      </c>
-      <c r="CF14">
-        <v>1.91</v>
-      </c>
-      <c r="CG14">
-        <v>3.25</v>
-      </c>
-      <c r="CH14">
-        <v>4.33</v>
-      </c>
-      <c r="CJ14" t="s">
-        <v>360</v>
-      </c>
-      <c r="CM14" t="s">
-        <v>847</v>
-      </c>
-      <c r="CO14" t="s">
-        <v>848</v>
+        <v>753</v>
       </c>
     </row>
-    <row r="15" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>849</v>
+        <v>754</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -7425,267 +6145,201 @@
         <v>45081.458333333343</v>
       </c>
       <c r="G15" t="s">
-        <v>368</v>
+        <v>316</v>
       </c>
       <c r="H15" t="s">
-        <v>850</v>
+        <v>755</v>
       </c>
       <c r="I15" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="J15" t="s">
-        <v>118</v>
+        <v>756</v>
       </c>
       <c r="K15" t="s">
-        <v>242</v>
+        <v>330</v>
       </c>
       <c r="L15" t="s">
-        <v>851</v>
-      </c>
-      <c r="M15" s="3">
-        <v>51</v>
-      </c>
-      <c r="N15" s="3">
-        <v>49</v>
+        <v>363</v>
+      </c>
+      <c r="M15" t="s">
+        <v>332</v>
+      </c>
+      <c r="N15" t="s">
+        <v>333</v>
       </c>
       <c r="O15" t="s">
-        <v>179</v>
+        <v>334</v>
       </c>
       <c r="P15" t="s">
-        <v>179</v>
+        <v>335</v>
       </c>
       <c r="Q15" t="s">
-        <v>309</v>
+        <v>340</v>
       </c>
       <c r="R15" t="s">
-        <v>241</v>
+        <v>336</v>
       </c>
       <c r="S15" t="s">
-        <v>116</v>
+        <v>337</v>
       </c>
       <c r="T15" t="s">
-        <v>116</v>
+        <v>338</v>
       </c>
       <c r="U15" t="s">
-        <v>112</v>
+        <v>339</v>
       </c>
       <c r="V15" t="s">
-        <v>435</v>
+        <v>757</v>
       </c>
       <c r="W15" t="s">
-        <v>852</v>
+        <v>758</v>
       </c>
       <c r="X15" t="s">
-        <v>853</v>
+        <v>759</v>
       </c>
       <c r="Y15" t="s">
-        <v>854</v>
+        <v>760</v>
       </c>
       <c r="Z15" t="s">
-        <v>855</v>
+        <v>761</v>
       </c>
       <c r="AA15" t="s">
-        <v>118</v>
+        <v>762</v>
       </c>
       <c r="AB15" t="s">
-        <v>118</v>
+        <v>763</v>
       </c>
       <c r="AC15" t="s">
-        <v>183</v>
+        <v>764</v>
       </c>
       <c r="AD15" t="s">
-        <v>856</v>
+        <v>765</v>
       </c>
       <c r="AE15" t="s">
-        <v>437</v>
+        <v>766</v>
       </c>
       <c r="AF15" t="s">
-        <v>552</v>
+        <v>767</v>
       </c>
       <c r="AG15" t="s">
-        <v>388</v>
+        <v>349</v>
       </c>
       <c r="AH15" t="s">
-        <v>421</v>
+        <v>350</v>
       </c>
       <c r="AI15" t="s">
-        <v>390</v>
+        <v>768</v>
       </c>
       <c r="AJ15" t="s">
-        <v>391</v>
+        <v>351</v>
       </c>
       <c r="AK15" t="s">
-        <v>392</v>
+        <v>353</v>
       </c>
       <c r="AL15" t="s">
-        <v>393</v>
+        <v>354</v>
       </c>
       <c r="AM15" t="s">
-        <v>398</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>394</v>
+        <v>355</v>
       </c>
       <c r="AO15" t="s">
-        <v>395</v>
+        <v>769</v>
       </c>
       <c r="AP15" t="s">
-        <v>396</v>
+        <v>770</v>
       </c>
       <c r="AQ15" t="s">
-        <v>397</v>
+        <v>771</v>
       </c>
       <c r="AR15" t="s">
-        <v>857</v>
+        <v>772</v>
       </c>
       <c r="AS15" t="s">
-        <v>858</v>
+        <v>773</v>
       </c>
       <c r="AT15" t="s">
-        <v>859</v>
+        <v>774</v>
       </c>
       <c r="AU15" t="s">
-        <v>860</v>
+        <v>775</v>
       </c>
       <c r="AV15" t="s">
-        <v>861</v>
+        <v>360</v>
       </c>
       <c r="AW15" t="s">
-        <v>862</v>
+        <v>361</v>
       </c>
       <c r="AX15" t="s">
-        <v>863</v>
+        <v>352</v>
       </c>
       <c r="AY15" t="s">
-        <v>864</v>
+        <v>362</v>
       </c>
       <c r="AZ15" t="s">
-        <v>865</v>
+        <v>776</v>
       </c>
       <c r="BA15" t="s">
-        <v>866</v>
+        <v>777</v>
       </c>
       <c r="BB15" t="s">
-        <v>867</v>
+        <v>778</v>
       </c>
       <c r="BC15" t="s">
-        <v>407</v>
-      </c>
-      <c r="BD15" t="s">
-        <v>408</v>
+        <v>779</v>
       </c>
       <c r="BE15" t="s">
-        <v>868</v>
+        <v>780</v>
       </c>
       <c r="BF15" t="s">
-        <v>409</v>
+        <v>781</v>
       </c>
       <c r="BG15" t="s">
-        <v>411</v>
+        <v>782</v>
       </c>
       <c r="BH15" t="s">
-        <v>412</v>
+        <v>366</v>
       </c>
       <c r="BI15" t="s">
-        <v>413</v>
-      </c>
-      <c r="BK15" t="s">
-        <v>869</v>
-      </c>
-      <c r="BL15" t="s">
-        <v>870</v>
+        <v>783</v>
+      </c>
+      <c r="BJ15">
+        <v>2.1</v>
+      </c>
+      <c r="BK15">
+        <v>3.2</v>
+      </c>
+      <c r="BL15">
+        <v>3.6</v>
       </c>
       <c r="BM15" t="s">
-        <v>871</v>
+        <v>370</v>
       </c>
       <c r="BN15" t="s">
-        <v>872</v>
+        <v>364</v>
       </c>
       <c r="BO15" t="s">
-        <v>873</v>
-      </c>
-      <c r="BP15" t="s">
-        <v>874</v>
+        <v>331</v>
       </c>
       <c r="BQ15" t="s">
-        <v>875</v>
-      </c>
-      <c r="BR15" t="s">
-        <v>418</v>
+        <v>784</v>
       </c>
       <c r="BS15" t="s">
-        <v>419</v>
-      </c>
-      <c r="BT15" t="s">
-        <v>410</v>
-      </c>
-      <c r="BU15" t="s">
-        <v>420</v>
-      </c>
-      <c r="BV15" t="s">
-        <v>876</v>
-      </c>
-      <c r="BW15" t="s">
-        <v>877</v>
-      </c>
-      <c r="BX15" t="s">
-        <v>878</v>
-      </c>
-      <c r="BY15" t="s">
-        <v>879</v>
-      </c>
-      <c r="CA15" t="s">
-        <v>880</v>
-      </c>
-      <c r="CB15" t="s">
-        <v>881</v>
-      </c>
-      <c r="CC15" t="s">
-        <v>882</v>
-      </c>
-      <c r="CD15" t="s">
-        <v>424</v>
-      </c>
-      <c r="CE15" t="s">
-        <v>883</v>
-      </c>
-      <c r="CF15">
-        <v>2.1</v>
-      </c>
-      <c r="CG15">
-        <v>3.2</v>
-      </c>
-      <c r="CH15">
-        <v>3.6</v>
-      </c>
-      <c r="CI15" t="s">
-        <v>428</v>
-      </c>
-      <c r="CJ15" t="s">
-        <v>422</v>
-      </c>
-      <c r="CK15" t="s">
-        <v>389</v>
-      </c>
-      <c r="CM15" t="s">
-        <v>884</v>
-      </c>
-      <c r="CO15" t="s">
-        <v>885</v>
+        <v>785</v>
       </c>
     </row>
-    <row r="16" spans="1:103" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:81" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>886</v>
+        <v>786</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -7694,267 +6348,201 @@
         <v>45080.895833333343</v>
       </c>
       <c r="G16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" t="s">
+        <v>198</v>
+      </c>
+      <c r="I16" t="s">
+        <v>546</v>
+      </c>
+      <c r="J16" t="s">
+        <v>787</v>
+      </c>
+      <c r="K16" t="s">
+        <v>788</v>
+      </c>
+      <c r="L16" t="s">
+        <v>104</v>
+      </c>
+      <c r="M16" t="s">
+        <v>789</v>
+      </c>
+      <c r="N16" t="s">
+        <v>102</v>
+      </c>
+      <c r="O16" t="s">
+        <v>107</v>
+      </c>
+      <c r="P16" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>122</v>
+      </c>
+      <c r="R16" t="s">
+        <v>106</v>
+      </c>
+      <c r="S16" t="s">
+        <v>790</v>
+      </c>
+      <c r="T16" t="s">
+        <v>791</v>
+      </c>
+      <c r="U16" t="s">
         <v>108</v>
       </c>
-      <c r="H16" t="s">
+      <c r="V16" t="s">
+        <v>202</v>
+      </c>
+      <c r="W16" t="s">
+        <v>203</v>
+      </c>
+      <c r="X16" t="s">
+        <v>204</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>242</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>205</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>207</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>208</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>211</v>
+      </c>
+      <c r="AE16" t="s">
         <v>239</v>
       </c>
-      <c r="I16" t="s">
-        <v>114</v>
-      </c>
-      <c r="J16" t="s">
-        <v>118</v>
-      </c>
-      <c r="K16" t="s">
-        <v>613</v>
-      </c>
-      <c r="L16" t="s">
-        <v>887</v>
-      </c>
-      <c r="M16" s="3">
-        <v>62</v>
-      </c>
-      <c r="N16" s="3">
-        <v>38</v>
-      </c>
-      <c r="O16" t="s">
-        <v>117</v>
-      </c>
-      <c r="P16" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q16" t="s">
+      <c r="AF16" t="s">
+        <v>212</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>130</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>133</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>124</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>100</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>125</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>792</v>
+      </c>
+      <c r="AP16" t="s">
+        <v>225</v>
+      </c>
+      <c r="AQ16" t="s">
+        <v>793</v>
+      </c>
+      <c r="AR16" t="s">
+        <v>228</v>
+      </c>
+      <c r="AS16" t="s">
+        <v>229</v>
+      </c>
+      <c r="AT16" t="s">
+        <v>230</v>
+      </c>
+      <c r="AU16" t="s">
+        <v>231</v>
+      </c>
+      <c r="AV16" t="s">
+        <v>105</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>103</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>131</v>
+      </c>
+      <c r="AY16" t="s">
+        <v>134</v>
+      </c>
+      <c r="AZ16" t="s">
+        <v>226</v>
+      </c>
+      <c r="BA16" t="s">
         <v>241</v>
       </c>
-      <c r="R16" t="s">
-        <v>116</v>
-      </c>
-      <c r="S16" t="s">
-        <v>116</v>
-      </c>
-      <c r="T16" t="s">
-        <v>241</v>
-      </c>
-      <c r="U16" t="s">
-        <v>181</v>
-      </c>
-      <c r="V16" t="s">
-        <v>112</v>
-      </c>
-      <c r="W16" t="s">
-        <v>888</v>
-      </c>
-      <c r="X16" t="s">
-        <v>889</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>890</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>891</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>116</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>437</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>245</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>121</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>246</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>892</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>138</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>893</v>
-      </c>
-      <c r="AJ16" t="s">
+      <c r="BB16" t="s">
+        <v>794</v>
+      </c>
+      <c r="BC16" t="s">
+        <v>227</v>
+      </c>
+      <c r="BD16" t="s">
+        <v>240</v>
+      </c>
+      <c r="BE16" t="s">
+        <v>253</v>
+      </c>
+      <c r="BF16" t="s">
+        <v>254</v>
+      </c>
+      <c r="BG16" t="s">
+        <v>795</v>
+      </c>
+      <c r="BH16" t="s">
+        <v>139</v>
+      </c>
+      <c r="BI16" t="s">
+        <v>251</v>
+      </c>
+      <c r="BJ16">
+        <v>1.95</v>
+      </c>
+      <c r="BK16">
+        <v>3.3</v>
+      </c>
+      <c r="BL16">
+        <v>4</v>
+      </c>
+      <c r="BN16" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO16" t="s">
         <v>136</v>
       </c>
-      <c r="AK16" t="s">
-        <v>141</v>
-      </c>
-      <c r="AL16" t="s">
-        <v>144</v>
-      </c>
-      <c r="AM16" t="s">
-        <v>156</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>140</v>
-      </c>
-      <c r="AO16" t="s">
-        <v>894</v>
-      </c>
-      <c r="AP16" t="s">
-        <v>895</v>
-      </c>
-      <c r="AQ16" t="s">
-        <v>142</v>
-      </c>
-      <c r="AR16" t="s">
-        <v>248</v>
-      </c>
-      <c r="AS16" t="s">
-        <v>249</v>
-      </c>
-      <c r="AT16" t="s">
-        <v>250</v>
-      </c>
-      <c r="AU16" t="s">
-        <v>288</v>
-      </c>
-      <c r="AV16" t="s">
-        <v>251</v>
-      </c>
-      <c r="AW16" t="s">
-        <v>255</v>
-      </c>
-      <c r="AX16" t="s">
-        <v>253</v>
-      </c>
-      <c r="AY16" t="s">
-        <v>254</v>
-      </c>
-      <c r="AZ16" t="s">
-        <v>257</v>
-      </c>
-      <c r="BA16" t="s">
-        <v>285</v>
-      </c>
-      <c r="BB16" t="s">
-        <v>258</v>
-      </c>
-      <c r="BC16" t="s">
-        <v>154</v>
-      </c>
-      <c r="BD16" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE16" t="s">
-        <v>164</v>
-      </c>
-      <c r="BF16" t="s">
-        <v>167</v>
-      </c>
-      <c r="BG16" t="s">
-        <v>157</v>
-      </c>
-      <c r="BH16" t="s">
-        <v>158</v>
-      </c>
-      <c r="BI16" t="s">
-        <v>134</v>
-      </c>
-      <c r="BJ16" t="s">
-        <v>159</v>
-      </c>
-      <c r="BK16" t="s">
-        <v>896</v>
-      </c>
-      <c r="BL16" t="s">
-        <v>271</v>
-      </c>
-      <c r="BM16" t="s">
-        <v>897</v>
-      </c>
-      <c r="BN16" t="s">
-        <v>274</v>
-      </c>
-      <c r="BO16" t="s">
-        <v>275</v>
-      </c>
       <c r="BP16" t="s">
-        <v>276</v>
-      </c>
-      <c r="BQ16" t="s">
-        <v>277</v>
-      </c>
-      <c r="BR16" t="s">
-        <v>139</v>
-      </c>
-      <c r="BS16" t="s">
         <v>137</v>
       </c>
-      <c r="BT16" t="s">
-        <v>165</v>
-      </c>
-      <c r="BU16" t="s">
-        <v>168</v>
-      </c>
-      <c r="BV16" t="s">
-        <v>272</v>
-      </c>
-      <c r="BW16" t="s">
-        <v>287</v>
-      </c>
-      <c r="BX16" t="s">
-        <v>898</v>
-      </c>
-      <c r="BY16" t="s">
-        <v>273</v>
-      </c>
-      <c r="BZ16" t="s">
-        <v>286</v>
-      </c>
-      <c r="CA16" t="s">
-        <v>299</v>
-      </c>
-      <c r="CB16" t="s">
-        <v>300</v>
-      </c>
-      <c r="CC16" t="s">
-        <v>899</v>
-      </c>
-      <c r="CD16" t="s">
-        <v>173</v>
-      </c>
-      <c r="CE16" t="s">
-        <v>297</v>
-      </c>
-      <c r="CF16">
-        <v>1.95</v>
-      </c>
-      <c r="CG16">
-        <v>3.3</v>
-      </c>
-      <c r="CH16">
-        <v>4</v>
-      </c>
-      <c r="CJ16" t="s">
-        <v>169</v>
-      </c>
-      <c r="CK16" t="s">
-        <v>170</v>
-      </c>
-      <c r="CL16" t="s">
-        <v>171</v>
-      </c>
     </row>
-    <row r="17" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>900</v>
+        <v>796</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -7963,258 +6551,192 @@
         <v>45080.791666666657</v>
       </c>
       <c r="G17" t="s">
+        <v>259</v>
+      </c>
+      <c r="H17" t="s">
+        <v>797</v>
+      </c>
+      <c r="I17" t="s">
+        <v>317</v>
+      </c>
+      <c r="J17" t="s">
+        <v>798</v>
+      </c>
+      <c r="K17" t="s">
+        <v>273</v>
+      </c>
+      <c r="L17" t="s">
+        <v>274</v>
+      </c>
+      <c r="M17" t="s">
+        <v>275</v>
+      </c>
+      <c r="N17" t="s">
+        <v>276</v>
+      </c>
+      <c r="O17" t="s">
+        <v>277</v>
+      </c>
+      <c r="P17" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>279</v>
+      </c>
+      <c r="R17" t="s">
+        <v>280</v>
+      </c>
+      <c r="S17" t="s">
+        <v>304</v>
+      </c>
+      <c r="T17" t="s">
+        <v>282</v>
+      </c>
+      <c r="U17" t="s">
+        <v>283</v>
+      </c>
+      <c r="V17" t="s">
+        <v>799</v>
+      </c>
+      <c r="W17" t="s">
+        <v>800</v>
+      </c>
+      <c r="X17" t="s">
+        <v>801</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>802</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>803</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>804</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>805</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>806</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>807</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>808</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>809</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>292</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>293</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>295</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>296</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>297</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>810</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>298</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>811</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>812</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>813</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>814</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>815</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>816</v>
+      </c>
+      <c r="AU17" t="s">
+        <v>817</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>281</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>302</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>313</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>818</v>
+      </c>
+      <c r="BA17" t="s">
+        <v>819</v>
+      </c>
+      <c r="BB17" t="s">
+        <v>820</v>
+      </c>
+      <c r="BE17" t="s">
+        <v>821</v>
+      </c>
+      <c r="BF17" t="s">
+        <v>822</v>
+      </c>
+      <c r="BH17" t="s">
+        <v>307</v>
+      </c>
+      <c r="BI17" t="s">
+        <v>823</v>
+      </c>
+      <c r="BJ17">
+        <v>2.75</v>
+      </c>
+      <c r="BK17">
+        <v>3</v>
+      </c>
+      <c r="BL17">
+        <v>2.75</v>
+      </c>
+      <c r="BN17" t="s">
         <v>305</v>
       </c>
-      <c r="H17" t="s">
-        <v>901</v>
-      </c>
-      <c r="I17" t="s">
-        <v>114</v>
-      </c>
-      <c r="J17" t="s">
-        <v>118</v>
-      </c>
-      <c r="K17" t="s">
-        <v>369</v>
-      </c>
-      <c r="L17" t="s">
-        <v>902</v>
-      </c>
-      <c r="M17" s="3">
-        <v>36</v>
-      </c>
-      <c r="N17" s="3">
-        <v>64</v>
-      </c>
-      <c r="O17" t="s">
-        <v>180</v>
-      </c>
-      <c r="P17" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>309</v>
-      </c>
-      <c r="R17" t="s">
-        <v>118</v>
-      </c>
-      <c r="S17" t="s">
-        <v>109</v>
-      </c>
-      <c r="T17" t="s">
-        <v>109</v>
-      </c>
-      <c r="U17" t="s">
-        <v>372</v>
-      </c>
-      <c r="V17" t="s">
-        <v>115</v>
-      </c>
-      <c r="W17" t="s">
-        <v>903</v>
-      </c>
-      <c r="X17" t="s">
-        <v>904</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>906</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>907</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>908</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>247</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>743</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>325</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>326</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>327</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>328</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>329</v>
-      </c>
-      <c r="AL17" t="s">
-        <v>330</v>
-      </c>
-      <c r="AM17" t="s">
-        <v>331</v>
-      </c>
-      <c r="AN17" t="s">
-        <v>332</v>
-      </c>
-      <c r="AO17" t="s">
-        <v>356</v>
-      </c>
-      <c r="AP17" t="s">
-        <v>334</v>
-      </c>
-      <c r="AQ17" t="s">
-        <v>335</v>
-      </c>
-      <c r="AR17" t="s">
-        <v>909</v>
-      </c>
-      <c r="AS17" t="s">
-        <v>910</v>
-      </c>
-      <c r="AT17" t="s">
-        <v>911</v>
-      </c>
-      <c r="AU17" t="s">
-        <v>912</v>
-      </c>
-      <c r="AV17" t="s">
-        <v>913</v>
-      </c>
-      <c r="AW17" t="s">
-        <v>914</v>
-      </c>
-      <c r="AX17" t="s">
-        <v>915</v>
-      </c>
-      <c r="AY17" t="s">
-        <v>916</v>
-      </c>
-      <c r="AZ17" t="s">
-        <v>917</v>
-      </c>
-      <c r="BA17" t="s">
-        <v>918</v>
-      </c>
-      <c r="BB17" t="s">
-        <v>919</v>
-      </c>
-      <c r="BC17" t="s">
-        <v>344</v>
-      </c>
-      <c r="BD17" t="s">
-        <v>345</v>
-      </c>
-      <c r="BE17" t="s">
-        <v>347</v>
-      </c>
-      <c r="BF17" t="s">
-        <v>348</v>
-      </c>
-      <c r="BG17" t="s">
-        <v>349</v>
-      </c>
-      <c r="BH17" t="s">
-        <v>920</v>
-      </c>
-      <c r="BI17" t="s">
-        <v>350</v>
-      </c>
-      <c r="BJ17" t="s">
-        <v>355</v>
-      </c>
-      <c r="BK17" t="s">
-        <v>921</v>
-      </c>
-      <c r="BL17" t="s">
-        <v>922</v>
-      </c>
-      <c r="BM17" t="s">
-        <v>923</v>
-      </c>
-      <c r="BN17" t="s">
-        <v>924</v>
-      </c>
-      <c r="BO17" t="s">
-        <v>925</v>
-      </c>
-      <c r="BP17" t="s">
-        <v>926</v>
-      </c>
-      <c r="BQ17" t="s">
-        <v>927</v>
-      </c>
       <c r="BR17" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="BS17" t="s">
-        <v>354</v>
+        <v>824</v>
       </c>
       <c r="BT17" t="s">
-        <v>365</v>
-      </c>
-      <c r="BV17" t="s">
-        <v>928</v>
-      </c>
-      <c r="BW17" t="s">
-        <v>929</v>
-      </c>
-      <c r="BX17" t="s">
-        <v>930</v>
-      </c>
-      <c r="CA17" t="s">
-        <v>931</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>932</v>
-      </c>
-      <c r="CD17" t="s">
-        <v>359</v>
-      </c>
-      <c r="CE17" t="s">
-        <v>933</v>
-      </c>
-      <c r="CF17">
-        <v>2.75</v>
-      </c>
-      <c r="CG17">
-        <v>3</v>
-      </c>
-      <c r="CH17">
-        <v>2.75</v>
-      </c>
-      <c r="CJ17" t="s">
-        <v>357</v>
-      </c>
-      <c r="CN17" t="s">
-        <v>364</v>
-      </c>
-      <c r="CO17" t="s">
-        <v>934</v>
-      </c>
-      <c r="CP17" t="s">
-        <v>935</v>
+        <v>825</v>
       </c>
     </row>
-    <row r="18" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>936</v>
+        <v>826</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -8223,261 +6745,195 @@
         <v>45080.791666666657</v>
       </c>
       <c r="G18" t="s">
-        <v>675</v>
+        <v>605</v>
       </c>
       <c r="H18" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I18" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="J18" t="s">
-        <v>109</v>
+        <v>827</v>
       </c>
       <c r="K18" t="s">
-        <v>306</v>
+        <v>619</v>
       </c>
       <c r="L18" t="s">
-        <v>937</v>
-      </c>
-      <c r="M18" s="3">
-        <v>39</v>
-      </c>
-      <c r="N18" s="3">
-        <v>61</v>
+        <v>650</v>
+      </c>
+      <c r="M18" t="s">
+        <v>621</v>
+      </c>
+      <c r="N18" t="s">
+        <v>622</v>
       </c>
       <c r="O18" t="s">
-        <v>938</v>
+        <v>162</v>
       </c>
       <c r="P18" t="s">
-        <v>179</v>
+        <v>623</v>
       </c>
       <c r="Q18" t="s">
-        <v>180</v>
+        <v>624</v>
       </c>
       <c r="R18" t="s">
+        <v>625</v>
+      </c>
+      <c r="S18" t="s">
+        <v>626</v>
+      </c>
+      <c r="T18" t="s">
+        <v>627</v>
+      </c>
+      <c r="U18" t="s">
+        <v>628</v>
+      </c>
+      <c r="V18" t="s">
+        <v>89</v>
+      </c>
+      <c r="W18" t="s">
+        <v>90</v>
+      </c>
+      <c r="X18" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>637</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>639</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>647</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>649</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>642</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>643</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>658</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>828</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>129</v>
+      </c>
+      <c r="AQ18" t="s">
+        <v>829</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>127</v>
+      </c>
+      <c r="AS18" t="s">
+        <v>115</v>
+      </c>
+      <c r="AT18" t="s">
         <v>116</v>
       </c>
-      <c r="S18" t="s">
-        <v>109</v>
-      </c>
-      <c r="T18" t="s">
-        <v>116</v>
-      </c>
-      <c r="U18" t="s">
-        <v>179</v>
-      </c>
-      <c r="V18" t="s">
-        <v>308</v>
-      </c>
-      <c r="W18" t="s">
-        <v>939</v>
-      </c>
-      <c r="X18" t="s">
-        <v>940</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>941</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>942</v>
-      </c>
-      <c r="AA18" t="s">
+      <c r="AU18" t="s">
+        <v>117</v>
+      </c>
+      <c r="AV18" t="s">
+        <v>620</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>648</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>659</v>
+      </c>
+      <c r="AY18" t="s">
+        <v>638</v>
+      </c>
+      <c r="AZ18" t="s">
+        <v>113</v>
+      </c>
+      <c r="BA18" t="s">
         <v>114</v>
       </c>
-      <c r="AB18" t="s">
-        <v>109</v>
-      </c>
-      <c r="AC18" t="s">
-        <v>943</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>944</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>375</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>945</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>692</v>
-      </c>
-      <c r="AH18" t="s">
-        <v>723</v>
-      </c>
-      <c r="AI18" t="s">
-        <v>694</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>695</v>
-      </c>
-      <c r="AK18" t="s">
-        <v>203</v>
-      </c>
-      <c r="AL18" t="s">
-        <v>696</v>
-      </c>
-      <c r="AM18" t="s">
-        <v>697</v>
-      </c>
-      <c r="AN18" t="s">
-        <v>698</v>
-      </c>
-      <c r="AO18" t="s">
-        <v>699</v>
-      </c>
-      <c r="AP18" t="s">
-        <v>700</v>
-      </c>
-      <c r="AQ18" t="s">
-        <v>701</v>
-      </c>
-      <c r="AR18" t="s">
-        <v>123</v>
-      </c>
-      <c r="AS18" t="s">
-        <v>124</v>
-      </c>
-      <c r="AT18" t="s">
-        <v>125</v>
-      </c>
-      <c r="AU18" t="s">
+      <c r="BB18" t="s">
         <v>126</v>
       </c>
-      <c r="AV18" t="s">
-        <v>127</v>
-      </c>
-      <c r="AW18" t="s">
-        <v>128</v>
-      </c>
-      <c r="AX18" t="s">
-        <v>129</v>
-      </c>
-      <c r="AY18" t="s">
-        <v>162</v>
-      </c>
-      <c r="AZ18" t="s">
-        <v>130</v>
-      </c>
-      <c r="BA18" t="s">
-        <v>132</v>
-      </c>
-      <c r="BB18" t="s">
-        <v>133</v>
-      </c>
-      <c r="BC18" t="s">
-        <v>710</v>
-      </c>
-      <c r="BD18" t="s">
-        <v>712</v>
-      </c>
       <c r="BE18" t="s">
-        <v>720</v>
+        <v>111</v>
       </c>
       <c r="BF18" t="s">
-        <v>722</v>
-      </c>
-      <c r="BG18" t="s">
-        <v>715</v>
+        <v>112</v>
       </c>
       <c r="BH18" t="s">
-        <v>716</v>
+        <v>654</v>
       </c>
       <c r="BI18" t="s">
-        <v>731</v>
-      </c>
-      <c r="BK18" t="s">
-        <v>946</v>
-      </c>
-      <c r="BL18" t="s">
-        <v>163</v>
+        <v>830</v>
+      </c>
+      <c r="BJ18">
+        <v>2.15</v>
+      </c>
+      <c r="BK18">
+        <v>3</v>
+      </c>
+      <c r="BL18">
+        <v>3.75</v>
       </c>
       <c r="BM18" t="s">
-        <v>947</v>
+        <v>641</v>
       </c>
       <c r="BN18" t="s">
-        <v>161</v>
+        <v>651</v>
       </c>
       <c r="BO18" t="s">
-        <v>149</v>
-      </c>
-      <c r="BP18" t="s">
-        <v>150</v>
-      </c>
-      <c r="BQ18" t="s">
-        <v>151</v>
-      </c>
-      <c r="BR18" t="s">
-        <v>693</v>
+        <v>652</v>
       </c>
       <c r="BS18" t="s">
-        <v>721</v>
+        <v>97</v>
       </c>
       <c r="BT18" t="s">
-        <v>732</v>
-      </c>
-      <c r="BU18" t="s">
-        <v>711</v>
-      </c>
-      <c r="BV18" t="s">
-        <v>147</v>
-      </c>
-      <c r="BW18" t="s">
-        <v>148</v>
-      </c>
-      <c r="BX18" t="s">
-        <v>160</v>
-      </c>
-      <c r="CA18" t="s">
-        <v>145</v>
-      </c>
-      <c r="CB18" t="s">
-        <v>146</v>
-      </c>
-      <c r="CD18" t="s">
-        <v>727</v>
-      </c>
-      <c r="CE18" t="s">
-        <v>948</v>
-      </c>
-      <c r="CF18">
-        <v>2.15</v>
-      </c>
-      <c r="CG18">
-        <v>3</v>
-      </c>
-      <c r="CH18">
-        <v>3.75</v>
-      </c>
-      <c r="CI18" t="s">
-        <v>714</v>
-      </c>
-      <c r="CJ18" t="s">
-        <v>724</v>
-      </c>
-      <c r="CK18" t="s">
-        <v>725</v>
-      </c>
-      <c r="CO18" t="s">
-        <v>131</v>
-      </c>
-      <c r="CP18" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>949</v>
+        <v>831</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -8486,264 +6942,198 @@
         <v>45080.583333333343</v>
       </c>
       <c r="G19" t="s">
-        <v>950</v>
+        <v>832</v>
       </c>
       <c r="H19" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="I19" t="s">
-        <v>114</v>
+        <v>375</v>
       </c>
       <c r="J19" t="s">
-        <v>118</v>
+        <v>833</v>
       </c>
       <c r="K19" t="s">
-        <v>433</v>
+        <v>834</v>
       </c>
       <c r="L19" t="s">
-        <v>951</v>
-      </c>
-      <c r="M19" s="3">
-        <v>42</v>
-      </c>
-      <c r="N19" s="3">
-        <v>58</v>
+        <v>835</v>
+      </c>
+      <c r="M19" t="s">
+        <v>836</v>
+      </c>
+      <c r="N19" t="s">
+        <v>837</v>
       </c>
       <c r="O19" t="s">
-        <v>112</v>
+        <v>838</v>
       </c>
       <c r="P19" t="s">
-        <v>179</v>
+        <v>839</v>
       </c>
       <c r="Q19" t="s">
-        <v>179</v>
+        <v>840</v>
       </c>
       <c r="R19" t="s">
-        <v>116</v>
+        <v>841</v>
       </c>
       <c r="S19" t="s">
-        <v>109</v>
+        <v>842</v>
       </c>
       <c r="T19" t="s">
-        <v>114</v>
+        <v>843</v>
       </c>
       <c r="U19" t="s">
-        <v>179</v>
+        <v>844</v>
       </c>
       <c r="V19" t="s">
-        <v>308</v>
+        <v>145</v>
       </c>
       <c r="W19" t="s">
-        <v>952</v>
+        <v>172</v>
       </c>
       <c r="X19" t="s">
-        <v>953</v>
+        <v>845</v>
       </c>
       <c r="Y19" t="s">
-        <v>954</v>
+        <v>148</v>
       </c>
       <c r="Z19" t="s">
-        <v>955</v>
+        <v>149</v>
       </c>
       <c r="AA19" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="AB19" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="AC19" t="s">
-        <v>907</v>
+        <v>150</v>
       </c>
       <c r="AD19" t="s">
-        <v>908</v>
+        <v>153</v>
       </c>
       <c r="AE19" t="s">
-        <v>247</v>
+        <v>182</v>
       </c>
       <c r="AF19" t="s">
-        <v>743</v>
+        <v>181</v>
       </c>
       <c r="AG19" t="s">
-        <v>956</v>
+        <v>846</v>
       </c>
       <c r="AH19" t="s">
-        <v>957</v>
+        <v>847</v>
       </c>
       <c r="AI19" t="s">
-        <v>958</v>
+        <v>848</v>
       </c>
       <c r="AJ19" t="s">
-        <v>959</v>
+        <v>849</v>
       </c>
       <c r="AK19" t="s">
-        <v>960</v>
+        <v>850</v>
       </c>
       <c r="AL19" t="s">
-        <v>961</v>
+        <v>851</v>
       </c>
       <c r="AM19" t="s">
-        <v>962</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>963</v>
+        <v>852</v>
       </c>
       <c r="AO19" t="s">
-        <v>964</v>
+        <v>167</v>
       </c>
       <c r="AP19" t="s">
-        <v>965</v>
+        <v>168</v>
       </c>
       <c r="AQ19" t="s">
-        <v>966</v>
+        <v>151</v>
       </c>
       <c r="AR19" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="AS19" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="AT19" t="s">
-        <v>967</v>
+        <v>853</v>
       </c>
       <c r="AU19" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AV19" t="s">
-        <v>190</v>
+        <v>854</v>
       </c>
       <c r="AW19" t="s">
-        <v>210</v>
+        <v>855</v>
       </c>
       <c r="AX19" t="s">
-        <v>211</v>
+        <v>856</v>
       </c>
       <c r="AY19" t="s">
-        <v>191</v>
+        <v>857</v>
       </c>
       <c r="AZ19" t="s">
+        <v>155</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>152</v>
+      </c>
+      <c r="BB19" t="s">
+        <v>183</v>
+      </c>
+      <c r="BC19" t="s">
+        <v>154</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>193</v>
+      </c>
+      <c r="BE19" t="s">
         <v>194</v>
       </c>
-      <c r="BA19" t="s">
-        <v>223</v>
-      </c>
-      <c r="BB19" t="s">
-        <v>222</v>
-      </c>
-      <c r="BC19" t="s">
-        <v>968</v>
-      </c>
-      <c r="BD19" t="s">
-        <v>969</v>
-      </c>
-      <c r="BE19" t="s">
-        <v>970</v>
-      </c>
       <c r="BF19" t="s">
-        <v>971</v>
+        <v>195</v>
       </c>
       <c r="BG19" t="s">
-        <v>972</v>
+        <v>196</v>
       </c>
       <c r="BH19" t="s">
-        <v>973</v>
+        <v>858</v>
       </c>
       <c r="BI19" t="s">
-        <v>974</v>
-      </c>
-      <c r="BK19" t="s">
-        <v>208</v>
-      </c>
-      <c r="BL19" t="s">
-        <v>209</v>
+        <v>859</v>
+      </c>
+      <c r="BJ19">
+        <v>2.4</v>
+      </c>
+      <c r="BK19">
+        <v>3</v>
+      </c>
+      <c r="BL19">
+        <v>3.2</v>
       </c>
       <c r="BM19" t="s">
-        <v>192</v>
+        <v>860</v>
       </c>
       <c r="BN19" t="s">
-        <v>212</v>
+        <v>861</v>
       </c>
       <c r="BO19" t="s">
-        <v>214</v>
-      </c>
-      <c r="BP19" t="s">
-        <v>975</v>
-      </c>
-      <c r="BQ19" t="s">
-        <v>225</v>
-      </c>
-      <c r="BR19" t="s">
-        <v>976</v>
-      </c>
-      <c r="BS19" t="s">
-        <v>977</v>
-      </c>
-      <c r="BT19" t="s">
-        <v>978</v>
-      </c>
-      <c r="BU19" t="s">
-        <v>979</v>
-      </c>
-      <c r="BV19" t="s">
-        <v>196</v>
-      </c>
-      <c r="BW19" t="s">
-        <v>193</v>
-      </c>
-      <c r="BX19" t="s">
-        <v>224</v>
-      </c>
-      <c r="BY19" t="s">
-        <v>195</v>
-      </c>
-      <c r="BZ19" t="s">
-        <v>234</v>
-      </c>
-      <c r="CA19" t="s">
-        <v>235</v>
-      </c>
-      <c r="CB19" t="s">
-        <v>236</v>
-      </c>
-      <c r="CC19" t="s">
-        <v>237</v>
-      </c>
-      <c r="CD19" t="s">
-        <v>980</v>
-      </c>
-      <c r="CE19" t="s">
-        <v>981</v>
-      </c>
-      <c r="CF19">
-        <v>2.4</v>
-      </c>
-      <c r="CG19">
-        <v>3</v>
-      </c>
-      <c r="CH19">
-        <v>3.2</v>
-      </c>
-      <c r="CI19" t="s">
-        <v>982</v>
-      </c>
-      <c r="CJ19" t="s">
-        <v>983</v>
-      </c>
-      <c r="CK19" t="s">
-        <v>984</v>
+        <v>862</v>
       </c>
     </row>
-    <row r="20" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>985</v>
+        <v>863</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -8752,249 +7142,183 @@
         <v>45079.895833333343</v>
       </c>
       <c r="G20" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" t="s">
+        <v>483</v>
+      </c>
+      <c r="I20" t="s">
+        <v>864</v>
+      </c>
+      <c r="J20" t="s">
+        <v>865</v>
+      </c>
+      <c r="K20" t="s">
+        <v>156</v>
+      </c>
+      <c r="L20" t="s">
+        <v>866</v>
+      </c>
+      <c r="M20" t="s">
+        <v>158</v>
+      </c>
+      <c r="N20" t="s">
+        <v>159</v>
+      </c>
+      <c r="O20" t="s">
+        <v>185</v>
+      </c>
+      <c r="P20" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>189</v>
+      </c>
+      <c r="R20" t="s">
+        <v>163</v>
+      </c>
+      <c r="S20" t="s">
+        <v>867</v>
+      </c>
+      <c r="T20" t="s">
+        <v>166</v>
+      </c>
+      <c r="U20" t="s">
+        <v>188</v>
+      </c>
+      <c r="V20" t="s">
+        <v>487</v>
+      </c>
+      <c r="W20" t="s">
+        <v>488</v>
+      </c>
+      <c r="X20" t="s">
+        <v>489</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>868</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>491</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>538</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>869</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>494</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>525</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>496</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>497</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>174</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>175</v>
+      </c>
+      <c r="AI20" t="s">
         <v>176</v>
       </c>
-      <c r="H20" t="s">
-        <v>548</v>
-      </c>
-      <c r="I20" t="s">
-        <v>109</v>
-      </c>
-      <c r="J20" t="s">
-        <v>118</v>
-      </c>
-      <c r="K20" t="s">
-        <v>986</v>
-      </c>
-      <c r="L20" t="s">
-        <v>987</v>
-      </c>
-      <c r="M20" s="3">
-        <v>60</v>
-      </c>
-      <c r="N20" s="3">
-        <v>40</v>
-      </c>
-      <c r="O20" t="s">
-        <v>244</v>
-      </c>
-      <c r="P20" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>241</v>
-      </c>
-      <c r="R20" t="s">
-        <v>114</v>
-      </c>
-      <c r="S20" t="s">
-        <v>309</v>
-      </c>
-      <c r="T20" t="s">
-        <v>115</v>
-      </c>
-      <c r="U20" t="s">
-        <v>117</v>
-      </c>
-      <c r="V20" t="s">
-        <v>308</v>
-      </c>
-      <c r="W20" t="s">
-        <v>988</v>
-      </c>
-      <c r="X20" t="s">
-        <v>905</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>989</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>990</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>109</v>
-      </c>
-      <c r="AC20" t="s">
-        <v>991</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>992</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>993</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>376</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>197</v>
-      </c>
-      <c r="AH20" t="s">
-        <v>994</v>
-      </c>
-      <c r="AI20" t="s">
-        <v>199</v>
-      </c>
       <c r="AJ20" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="AK20" t="s">
-        <v>226</v>
+        <v>180</v>
       </c>
       <c r="AL20" t="s">
-        <v>203</v>
+        <v>157</v>
       </c>
       <c r="AM20" t="s">
-        <v>230</v>
+        <v>164</v>
       </c>
       <c r="AN20" t="s">
-        <v>204</v>
+        <v>160</v>
       </c>
       <c r="AO20" t="s">
-        <v>995</v>
+        <v>509</v>
       </c>
       <c r="AP20" t="s">
-        <v>207</v>
+        <v>493</v>
       </c>
       <c r="AQ20" t="s">
-        <v>229</v>
+        <v>512</v>
       </c>
       <c r="AR20" t="s">
-        <v>554</v>
+        <v>492</v>
       </c>
       <c r="AS20" t="s">
-        <v>555</v>
+        <v>514</v>
       </c>
       <c r="AT20" t="s">
-        <v>556</v>
+        <v>490</v>
       </c>
       <c r="AU20" t="s">
-        <v>996</v>
+        <v>495</v>
       </c>
       <c r="AV20" t="s">
-        <v>558</v>
+        <v>178</v>
       </c>
       <c r="AW20" t="s">
-        <v>605</v>
+        <v>187</v>
       </c>
       <c r="AX20" t="s">
-        <v>997</v>
-      </c>
-      <c r="AY20" t="s">
-        <v>561</v>
+        <v>179</v>
       </c>
       <c r="AZ20" t="s">
-        <v>592</v>
+        <v>524</v>
       </c>
       <c r="BA20" t="s">
-        <v>563</v>
+        <v>523</v>
       </c>
       <c r="BB20" t="s">
-        <v>564</v>
+        <v>537</v>
       </c>
       <c r="BC20" t="s">
-        <v>215</v>
+        <v>536</v>
       </c>
       <c r="BD20" t="s">
-        <v>216</v>
-      </c>
-      <c r="BE20" t="s">
-        <v>217</v>
-      </c>
-      <c r="BF20" t="s">
-        <v>218</v>
-      </c>
-      <c r="BG20" t="s">
-        <v>221</v>
+        <v>511</v>
       </c>
       <c r="BH20" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="BI20" t="s">
-        <v>205</v>
-      </c>
-      <c r="BJ20" t="s">
-        <v>201</v>
-      </c>
-      <c r="BK20" t="s">
-        <v>576</v>
-      </c>
-      <c r="BL20" t="s">
-        <v>560</v>
-      </c>
-      <c r="BM20" t="s">
-        <v>579</v>
+        <v>534</v>
+      </c>
+      <c r="BJ20">
+        <v>1.62</v>
+      </c>
+      <c r="BK20">
+        <v>3.8</v>
+      </c>
+      <c r="BL20">
+        <v>5.25</v>
       </c>
       <c r="BN20" t="s">
-        <v>559</v>
-      </c>
-      <c r="BO20" t="s">
-        <v>581</v>
-      </c>
-      <c r="BP20" t="s">
-        <v>557</v>
-      </c>
-      <c r="BQ20" t="s">
-        <v>562</v>
-      </c>
-      <c r="BR20" t="s">
-        <v>219</v>
-      </c>
-      <c r="BS20" t="s">
-        <v>228</v>
-      </c>
-      <c r="BT20" t="s">
-        <v>220</v>
-      </c>
-      <c r="BV20" t="s">
-        <v>591</v>
-      </c>
-      <c r="BW20" t="s">
-        <v>590</v>
-      </c>
-      <c r="BX20" t="s">
-        <v>604</v>
-      </c>
-      <c r="BY20" t="s">
-        <v>603</v>
-      </c>
-      <c r="BZ20" t="s">
-        <v>578</v>
-      </c>
-      <c r="CD20" t="s">
-        <v>233</v>
-      </c>
-      <c r="CE20" t="s">
-        <v>601</v>
-      </c>
-      <c r="CF20">
-        <v>1.62</v>
-      </c>
-      <c r="CG20">
-        <v>3.8</v>
-      </c>
-      <c r="CH20">
-        <v>5.25</v>
-      </c>
-      <c r="CJ20" t="s">
-        <v>231</v>
+        <v>190</v>
       </c>
     </row>
-    <row r="21" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>998</v>
+        <v>870</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -9003,261 +7327,195 @@
         <v>45079.895833333343</v>
       </c>
       <c r="G21" t="s">
-        <v>549</v>
+        <v>484</v>
       </c>
       <c r="H21" t="s">
-        <v>431</v>
+        <v>373</v>
       </c>
       <c r="I21" t="s">
-        <v>109</v>
+        <v>871</v>
       </c>
       <c r="J21" t="s">
-        <v>116</v>
+        <v>872</v>
       </c>
       <c r="K21" t="s">
-        <v>999</v>
+        <v>498</v>
       </c>
       <c r="L21" t="s">
-        <v>1000</v>
-      </c>
-      <c r="M21" s="3">
-        <v>47</v>
-      </c>
-      <c r="N21" s="3">
-        <v>53</v>
+        <v>528</v>
+      </c>
+      <c r="M21" t="s">
+        <v>500</v>
+      </c>
+      <c r="N21" t="s">
+        <v>501</v>
       </c>
       <c r="O21" t="s">
-        <v>181</v>
+        <v>502</v>
       </c>
       <c r="P21" t="s">
-        <v>1001</v>
+        <v>503</v>
       </c>
       <c r="Q21" t="s">
-        <v>371</v>
+        <v>504</v>
       </c>
       <c r="R21" t="s">
-        <v>115</v>
+        <v>520</v>
       </c>
       <c r="S21" t="s">
-        <v>116</v>
+        <v>506</v>
       </c>
       <c r="T21" t="s">
-        <v>109</v>
+        <v>533</v>
       </c>
       <c r="U21" t="s">
-        <v>372</v>
+        <v>507</v>
       </c>
       <c r="V21" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="W21" t="s">
-        <v>1002</v>
+        <v>378</v>
       </c>
       <c r="X21" t="s">
-        <v>1003</v>
+        <v>379</v>
       </c>
       <c r="Y21" t="s">
-        <v>853</v>
+        <v>380</v>
       </c>
       <c r="Z21" t="s">
-        <v>988</v>
+        <v>381</v>
       </c>
       <c r="AA21" t="s">
-        <v>109</v>
+        <v>382</v>
       </c>
       <c r="AB21" t="s">
-        <v>241</v>
+        <v>383</v>
       </c>
       <c r="AC21" t="s">
-        <v>553</v>
+        <v>384</v>
       </c>
       <c r="AD21" t="s">
-        <v>1004</v>
+        <v>385</v>
       </c>
       <c r="AE21" t="s">
-        <v>313</v>
+        <v>386</v>
       </c>
       <c r="AF21" t="s">
-        <v>1005</v>
+        <v>387</v>
       </c>
       <c r="AG21" t="s">
-        <v>565</v>
+        <v>516</v>
       </c>
       <c r="AH21" t="s">
-        <v>595</v>
+        <v>508</v>
       </c>
       <c r="AI21" t="s">
-        <v>567</v>
+        <v>517</v>
       </c>
       <c r="AJ21" t="s">
-        <v>568</v>
+        <v>518</v>
       </c>
       <c r="AK21" t="s">
-        <v>569</v>
+        <v>499</v>
       </c>
       <c r="AL21" t="s">
-        <v>570</v>
+        <v>519</v>
       </c>
       <c r="AM21" t="s">
-        <v>571</v>
+        <v>521</v>
       </c>
       <c r="AN21" t="s">
-        <v>587</v>
+        <v>522</v>
       </c>
       <c r="AO21" t="s">
-        <v>573</v>
+        <v>399</v>
       </c>
       <c r="AP21" t="s">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AQ21" t="s">
-        <v>574</v>
+        <v>873</v>
       </c>
       <c r="AR21" t="s">
-        <v>439</v>
+        <v>401</v>
       </c>
       <c r="AS21" t="s">
-        <v>440</v>
+        <v>403</v>
       </c>
       <c r="AT21" t="s">
-        <v>441</v>
+        <v>404</v>
       </c>
       <c r="AU21" t="s">
-        <v>442</v>
+        <v>874</v>
       </c>
       <c r="AV21" t="s">
-        <v>443</v>
+        <v>875</v>
       </c>
       <c r="AW21" t="s">
-        <v>444</v>
+        <v>527</v>
       </c>
       <c r="AX21" t="s">
-        <v>445</v>
-      </c>
-      <c r="AY21" t="s">
-        <v>446</v>
+        <v>530</v>
       </c>
       <c r="AZ21" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="BA21" t="s">
-        <v>448</v>
+        <v>413</v>
       </c>
       <c r="BB21" t="s">
-        <v>449</v>
+        <v>415</v>
       </c>
       <c r="BC21" t="s">
-        <v>583</v>
+        <v>414</v>
       </c>
       <c r="BD21" t="s">
-        <v>575</v>
+        <v>405</v>
       </c>
       <c r="BE21" t="s">
-        <v>584</v>
+        <v>425</v>
       </c>
       <c r="BF21" t="s">
-        <v>585</v>
-      </c>
-      <c r="BG21" t="s">
-        <v>566</v>
+        <v>426</v>
       </c>
       <c r="BH21" t="s">
-        <v>586</v>
+        <v>535</v>
       </c>
       <c r="BI21" t="s">
-        <v>588</v>
-      </c>
-      <c r="BJ21" t="s">
-        <v>589</v>
-      </c>
-      <c r="BK21" t="s">
-        <v>461</v>
-      </c>
-      <c r="BL21" t="s">
-        <v>462</v>
-      </c>
-      <c r="BM21" t="s">
-        <v>1006</v>
+        <v>422</v>
+      </c>
+      <c r="BJ21">
+        <v>2.8</v>
+      </c>
+      <c r="BK21">
+        <v>3.2</v>
+      </c>
+      <c r="BL21">
+        <v>2.5499999999999998</v>
       </c>
       <c r="BN21" t="s">
-        <v>463</v>
+        <v>876</v>
       </c>
       <c r="BO21" t="s">
-        <v>465</v>
-      </c>
-      <c r="BP21" t="s">
-        <v>466</v>
-      </c>
-      <c r="BQ21" t="s">
-        <v>1007</v>
+        <v>532</v>
       </c>
       <c r="BR21" t="s">
-        <v>1008</v>
-      </c>
-      <c r="BS21" t="s">
-        <v>594</v>
-      </c>
-      <c r="BT21" t="s">
-        <v>597</v>
-      </c>
-      <c r="BV21" t="s">
-        <v>489</v>
-      </c>
-      <c r="BW21" t="s">
-        <v>475</v>
-      </c>
-      <c r="BX21" t="s">
-        <v>477</v>
-      </c>
-      <c r="BY21" t="s">
-        <v>476</v>
-      </c>
-      <c r="BZ21" t="s">
-        <v>467</v>
-      </c>
-      <c r="CA21" t="s">
-        <v>487</v>
-      </c>
-      <c r="CB21" t="s">
-        <v>488</v>
-      </c>
-      <c r="CD21" t="s">
-        <v>602</v>
-      </c>
-      <c r="CE21" t="s">
-        <v>484</v>
-      </c>
-      <c r="CF21">
-        <v>2.8</v>
-      </c>
-      <c r="CG21">
-        <v>3.2</v>
-      </c>
-      <c r="CH21">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="CJ21" t="s">
-        <v>1009</v>
-      </c>
-      <c r="CK21" t="s">
-        <v>599</v>
-      </c>
-      <c r="CN21" t="s">
-        <v>607</v>
+        <v>540</v>
       </c>
     </row>
-    <row r="22" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>1010</v>
+        <v>877</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -9266,276 +7524,210 @@
         <v>45079.791666666657</v>
       </c>
       <c r="G22" t="s">
-        <v>1011</v>
+        <v>878</v>
       </c>
       <c r="H22" t="s">
-        <v>674</v>
+        <v>604</v>
       </c>
       <c r="I22" t="s">
-        <v>309</v>
+        <v>431</v>
       </c>
       <c r="J22" t="s">
-        <v>114</v>
+        <v>879</v>
       </c>
       <c r="K22" t="s">
-        <v>493</v>
+        <v>880</v>
       </c>
       <c r="L22" t="s">
-        <v>1012</v>
-      </c>
-      <c r="M22" s="3">
-        <v>54</v>
-      </c>
-      <c r="N22" s="3">
-        <v>46</v>
+        <v>881</v>
+      </c>
+      <c r="M22" t="s">
+        <v>882</v>
+      </c>
+      <c r="N22" t="s">
+        <v>883</v>
       </c>
       <c r="O22" t="s">
-        <v>180</v>
+        <v>884</v>
       </c>
       <c r="P22" t="s">
-        <v>181</v>
+        <v>885</v>
       </c>
       <c r="Q22" t="s">
-        <v>435</v>
+        <v>886</v>
       </c>
       <c r="R22" t="s">
-        <v>115</v>
+        <v>887</v>
       </c>
       <c r="S22" t="s">
-        <v>109</v>
+        <v>888</v>
       </c>
       <c r="T22" t="s">
-        <v>114</v>
+        <v>889</v>
       </c>
       <c r="U22" t="s">
-        <v>180</v>
+        <v>890</v>
       </c>
       <c r="V22" t="s">
-        <v>435</v>
+        <v>657</v>
       </c>
       <c r="W22" t="s">
-        <v>1013</v>
+        <v>609</v>
       </c>
       <c r="X22" t="s">
-        <v>1014</v>
+        <v>611</v>
       </c>
       <c r="Y22" t="s">
-        <v>1015</v>
+        <v>610</v>
       </c>
       <c r="Z22" t="s">
-        <v>1016</v>
+        <v>633</v>
       </c>
       <c r="AA22" t="s">
-        <v>114</v>
+        <v>612</v>
       </c>
       <c r="AB22" t="s">
-        <v>118</v>
+        <v>613</v>
       </c>
       <c r="AC22" t="s">
-        <v>1017</v>
+        <v>634</v>
       </c>
       <c r="AD22" t="s">
-        <v>1018</v>
+        <v>615</v>
       </c>
       <c r="AE22" t="s">
-        <v>1019</v>
+        <v>616</v>
       </c>
       <c r="AF22" t="s">
-        <v>1020</v>
+        <v>618</v>
       </c>
       <c r="AG22" t="s">
-        <v>1021</v>
+        <v>891</v>
       </c>
       <c r="AH22" t="s">
-        <v>1022</v>
+        <v>892</v>
       </c>
       <c r="AI22" t="s">
-        <v>1023</v>
+        <v>893</v>
       </c>
       <c r="AJ22" t="s">
-        <v>1024</v>
+        <v>247</v>
       </c>
       <c r="AK22" t="s">
-        <v>1025</v>
+        <v>894</v>
       </c>
       <c r="AL22" t="s">
-        <v>1026</v>
+        <v>895</v>
       </c>
       <c r="AM22" t="s">
-        <v>1027</v>
-      </c>
-      <c r="AN22" t="s">
-        <v>1028</v>
+        <v>896</v>
       </c>
       <c r="AO22" t="s">
-        <v>1029</v>
+        <v>614</v>
       </c>
       <c r="AP22" t="s">
-        <v>1030</v>
+        <v>629</v>
       </c>
       <c r="AQ22" t="s">
-        <v>1031</v>
+        <v>630</v>
       </c>
       <c r="AR22" t="s">
-        <v>730</v>
+        <v>617</v>
       </c>
       <c r="AS22" t="s">
-        <v>682</v>
+        <v>897</v>
       </c>
       <c r="AT22" t="s">
-        <v>684</v>
+        <v>636</v>
       </c>
       <c r="AU22" t="s">
-        <v>683</v>
+        <v>645</v>
       </c>
       <c r="AV22" t="s">
-        <v>706</v>
+        <v>898</v>
       </c>
       <c r="AW22" t="s">
-        <v>685</v>
+        <v>899</v>
       </c>
       <c r="AX22" t="s">
-        <v>686</v>
+        <v>900</v>
       </c>
       <c r="AY22" t="s">
-        <v>707</v>
+        <v>901</v>
       </c>
       <c r="AZ22" t="s">
-        <v>688</v>
+        <v>631</v>
       </c>
       <c r="BA22" t="s">
-        <v>689</v>
+        <v>646</v>
       </c>
       <c r="BB22" t="s">
-        <v>691</v>
+        <v>644</v>
       </c>
       <c r="BC22" t="s">
-        <v>1032</v>
+        <v>632</v>
       </c>
       <c r="BD22" t="s">
-        <v>1033</v>
+        <v>635</v>
       </c>
       <c r="BE22" t="s">
-        <v>1034</v>
+        <v>608</v>
       </c>
       <c r="BF22" t="s">
-        <v>293</v>
+        <v>655</v>
       </c>
       <c r="BG22" t="s">
-        <v>1035</v>
+        <v>902</v>
       </c>
       <c r="BH22" t="s">
-        <v>1036</v>
+        <v>903</v>
       </c>
       <c r="BI22" t="s">
-        <v>1037</v>
-      </c>
-      <c r="BK22" t="s">
-        <v>687</v>
-      </c>
-      <c r="BL22" t="s">
-        <v>702</v>
+        <v>653</v>
+      </c>
+      <c r="BJ22">
+        <v>1.53</v>
+      </c>
+      <c r="BK22">
+        <v>3.75</v>
+      </c>
+      <c r="BL22">
+        <v>5.75</v>
       </c>
       <c r="BM22" t="s">
-        <v>703</v>
+        <v>904</v>
       </c>
       <c r="BN22" t="s">
-        <v>690</v>
+        <v>905</v>
       </c>
       <c r="BO22" t="s">
-        <v>1038</v>
+        <v>906</v>
       </c>
       <c r="BP22" t="s">
-        <v>709</v>
+        <v>907</v>
       </c>
       <c r="BQ22" t="s">
-        <v>718</v>
-      </c>
-      <c r="BR22" t="s">
-        <v>1039</v>
-      </c>
-      <c r="BS22" t="s">
-        <v>1040</v>
-      </c>
-      <c r="BT22" t="s">
-        <v>1041</v>
-      </c>
-      <c r="BU22" t="s">
-        <v>1042</v>
+        <v>656</v>
       </c>
       <c r="BV22" t="s">
-        <v>704</v>
+        <v>908</v>
       </c>
       <c r="BW22" t="s">
-        <v>719</v>
-      </c>
-      <c r="BX22" t="s">
-        <v>717</v>
-      </c>
-      <c r="BY22" t="s">
-        <v>705</v>
-      </c>
-      <c r="BZ22" t="s">
-        <v>708</v>
-      </c>
-      <c r="CA22" t="s">
-        <v>681</v>
-      </c>
-      <c r="CB22" t="s">
-        <v>728</v>
-      </c>
-      <c r="CC22" t="s">
-        <v>1043</v>
-      </c>
-      <c r="CD22" t="s">
-        <v>1044</v>
-      </c>
-      <c r="CE22" t="s">
-        <v>726</v>
-      </c>
-      <c r="CF22">
-        <v>1.53</v>
-      </c>
-      <c r="CG22">
-        <v>3.75</v>
-      </c>
-      <c r="CH22">
-        <v>5.75</v>
-      </c>
-      <c r="CI22" t="s">
-        <v>1045</v>
-      </c>
-      <c r="CJ22" t="s">
-        <v>1046</v>
-      </c>
-      <c r="CK22" t="s">
-        <v>1047</v>
-      </c>
-      <c r="CL22" t="s">
-        <v>1048</v>
-      </c>
-      <c r="CM22" t="s">
-        <v>729</v>
-      </c>
-      <c r="CR22" t="s">
-        <v>1049</v>
-      </c>
-      <c r="CS22" t="s">
-        <v>1050</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="23" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>1051</v>
+        <v>910</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -9544,264 +7736,198 @@
         <v>45078.895833333343</v>
       </c>
       <c r="G23" t="s">
-        <v>432</v>
+        <v>374</v>
       </c>
       <c r="H23" t="s">
-        <v>491</v>
+        <v>429</v>
       </c>
       <c r="I23" t="s">
-        <v>109</v>
+        <v>911</v>
       </c>
       <c r="J23" t="s">
-        <v>118</v>
+        <v>912</v>
       </c>
       <c r="K23" t="s">
-        <v>1052</v>
+        <v>388</v>
       </c>
       <c r="L23" t="s">
-        <v>1053</v>
-      </c>
-      <c r="M23" s="3">
-        <v>26</v>
-      </c>
-      <c r="N23" s="3">
-        <v>74</v>
+        <v>389</v>
+      </c>
+      <c r="M23" t="s">
+        <v>390</v>
+      </c>
+      <c r="N23" t="s">
+        <v>392</v>
       </c>
       <c r="O23" t="s">
-        <v>309</v>
+        <v>913</v>
       </c>
       <c r="P23" t="s">
+        <v>417</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>394</v>
+      </c>
+      <c r="R23" t="s">
+        <v>391</v>
+      </c>
+      <c r="S23" t="s">
+        <v>396</v>
+      </c>
+      <c r="T23" t="s">
+        <v>398</v>
+      </c>
+      <c r="U23" t="s">
+        <v>397</v>
+      </c>
+      <c r="V23" t="s">
+        <v>461</v>
+      </c>
+      <c r="W23" t="s">
+        <v>914</v>
+      </c>
+      <c r="X23" t="s">
         <v>435</v>
       </c>
-      <c r="Q23" t="s">
-        <v>114</v>
-      </c>
-      <c r="R23" t="s">
-        <v>114</v>
-      </c>
-      <c r="S23" t="s">
-        <v>109</v>
-      </c>
-      <c r="T23" t="s">
-        <v>109</v>
-      </c>
-      <c r="U23" t="s">
-        <v>1054</v>
-      </c>
-      <c r="V23" t="s">
-        <v>179</v>
-      </c>
-      <c r="W23" t="s">
-        <v>1055</v>
-      </c>
-      <c r="X23" t="s">
-        <v>1056</v>
-      </c>
       <c r="Y23" t="s">
-        <v>1057</v>
+        <v>915</v>
       </c>
       <c r="Z23" t="s">
-        <v>1058</v>
+        <v>916</v>
       </c>
       <c r="AA23" t="s">
-        <v>116</v>
+        <v>917</v>
       </c>
       <c r="AB23" t="s">
-        <v>118</v>
+        <v>471</v>
       </c>
       <c r="AC23" t="s">
-        <v>1019</v>
+        <v>439</v>
       </c>
       <c r="AD23" t="s">
-        <v>1059</v>
+        <v>918</v>
       </c>
       <c r="AE23" t="s">
-        <v>736</v>
+        <v>919</v>
       </c>
       <c r="AF23" t="s">
+        <v>442</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>406</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>393</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>920</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>408</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>921</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>409</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>410</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>411</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>922</v>
+      </c>
+      <c r="AP23" t="s">
+        <v>433</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>456</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>457</v>
+      </c>
+      <c r="AS23" t="s">
+        <v>441</v>
+      </c>
+      <c r="AT23" t="s">
+        <v>460</v>
+      </c>
+      <c r="AU23" t="s">
+        <v>440</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>420</v>
+      </c>
+      <c r="AW23" t="s">
+        <v>418</v>
+      </c>
+      <c r="AX23" t="s">
+        <v>395</v>
+      </c>
+      <c r="AY23" t="s">
+        <v>419</v>
+      </c>
+      <c r="AZ23" t="s">
+        <v>436</v>
+      </c>
+      <c r="BA23" t="s">
+        <v>220</v>
+      </c>
+      <c r="BB23" t="s">
+        <v>923</v>
+      </c>
+      <c r="BE23" t="s">
+        <v>437</v>
+      </c>
+      <c r="BF23" t="s">
         <v>438</v>
       </c>
-      <c r="AG23" t="s">
-        <v>450</v>
-      </c>
-      <c r="AH23" t="s">
-        <v>451</v>
-      </c>
-      <c r="AI23" t="s">
-        <v>452</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>454</v>
-      </c>
-      <c r="AK23" t="s">
-        <v>1060</v>
-      </c>
-      <c r="AL23" t="s">
+      <c r="BG23" t="s">
         <v>479</v>
       </c>
-      <c r="AM23" t="s">
-        <v>456</v>
-      </c>
-      <c r="AN23" t="s">
-        <v>453</v>
-      </c>
-      <c r="AO23" t="s">
-        <v>458</v>
-      </c>
-      <c r="AP23" t="s">
-        <v>460</v>
-      </c>
-      <c r="AQ23" t="s">
-        <v>459</v>
-      </c>
-      <c r="AR23" t="s">
-        <v>526</v>
-      </c>
-      <c r="AS23" t="s">
-        <v>1061</v>
-      </c>
-      <c r="AT23" t="s">
-        <v>500</v>
-      </c>
-      <c r="AU23" t="s">
-        <v>1062</v>
-      </c>
-      <c r="AV23" t="s">
-        <v>1063</v>
-      </c>
-      <c r="AW23" t="s">
-        <v>1064</v>
-      </c>
-      <c r="AX23" t="s">
-        <v>536</v>
-      </c>
-      <c r="AY23" t="s">
-        <v>504</v>
-      </c>
-      <c r="AZ23" t="s">
-        <v>1065</v>
-      </c>
-      <c r="BA23" t="s">
-        <v>1066</v>
-      </c>
-      <c r="BB23" t="s">
-        <v>507</v>
-      </c>
-      <c r="BC23" t="s">
-        <v>468</v>
-      </c>
-      <c r="BD23" t="s">
-        <v>455</v>
-      </c>
-      <c r="BE23" t="s">
-        <v>1067</v>
-      </c>
-      <c r="BF23" t="s">
-        <v>470</v>
-      </c>
-      <c r="BG23" t="s">
-        <v>1068</v>
-      </c>
       <c r="BH23" t="s">
-        <v>471</v>
+        <v>423</v>
       </c>
       <c r="BI23" t="s">
+        <v>477</v>
+      </c>
+      <c r="BJ23">
+        <v>4.75</v>
+      </c>
+      <c r="BK23">
+        <v>3.4</v>
+      </c>
+      <c r="BL23">
+        <v>1.75</v>
+      </c>
+      <c r="BN23" t="s">
+        <v>421</v>
+      </c>
+      <c r="BQ23" t="s">
+        <v>480</v>
+      </c>
+      <c r="BS23" t="s">
+        <v>434</v>
+      </c>
+      <c r="BT23" t="s">
         <v>472</v>
       </c>
-      <c r="BJ23" t="s">
-        <v>473</v>
-      </c>
-      <c r="BK23" t="s">
-        <v>1069</v>
-      </c>
-      <c r="BL23" t="s">
-        <v>498</v>
-      </c>
-      <c r="BM23" t="s">
-        <v>521</v>
-      </c>
-      <c r="BN23" t="s">
-        <v>522</v>
-      </c>
-      <c r="BO23" t="s">
-        <v>506</v>
-      </c>
-      <c r="BP23" t="s">
-        <v>525</v>
-      </c>
-      <c r="BQ23" t="s">
-        <v>505</v>
-      </c>
-      <c r="BR23" t="s">
-        <v>482</v>
-      </c>
-      <c r="BS23" t="s">
-        <v>480</v>
-      </c>
-      <c r="BT23" t="s">
-        <v>457</v>
-      </c>
-      <c r="BU23" t="s">
-        <v>481</v>
-      </c>
-      <c r="BV23" t="s">
-        <v>501</v>
-      </c>
-      <c r="BW23" t="s">
-        <v>266</v>
-      </c>
-      <c r="BX23" t="s">
-        <v>1070</v>
-      </c>
-      <c r="CA23" t="s">
-        <v>502</v>
-      </c>
-      <c r="CB23" t="s">
-        <v>503</v>
-      </c>
-      <c r="CC23" t="s">
-        <v>544</v>
-      </c>
-      <c r="CD23" t="s">
-        <v>485</v>
-      </c>
-      <c r="CE23" t="s">
-        <v>542</v>
-      </c>
-      <c r="CF23">
-        <v>4.75</v>
-      </c>
-      <c r="CG23">
-        <v>3.4</v>
-      </c>
-      <c r="CH23">
-        <v>1.75</v>
-      </c>
-      <c r="CJ23" t="s">
-        <v>483</v>
-      </c>
-      <c r="CM23" t="s">
-        <v>545</v>
-      </c>
-      <c r="CO23" t="s">
-        <v>499</v>
-      </c>
-      <c r="CP23" t="s">
-        <v>537</v>
-      </c>
     </row>
-    <row r="24" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:75" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>1071</v>
+        <v>924</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -9810,280 +7936,214 @@
         <v>45078.833333333343</v>
       </c>
       <c r="G24" t="s">
-        <v>612</v>
+        <v>545</v>
       </c>
       <c r="H24" t="s">
+        <v>315</v>
+      </c>
+      <c r="I24" t="s">
+        <v>925</v>
+      </c>
+      <c r="J24" t="s">
+        <v>926</v>
+      </c>
+      <c r="K24" t="s">
+        <v>559</v>
+      </c>
+      <c r="L24" t="s">
+        <v>561</v>
+      </c>
+      <c r="M24" t="s">
+        <v>562</v>
+      </c>
+      <c r="N24" t="s">
+        <v>563</v>
+      </c>
+      <c r="O24" t="s">
+        <v>560</v>
+      </c>
+      <c r="P24" t="s">
+        <v>566</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>592</v>
+      </c>
+      <c r="R24" t="s">
+        <v>564</v>
+      </c>
+      <c r="S24" t="s">
+        <v>567</v>
+      </c>
+      <c r="T24" t="s">
+        <v>589</v>
+      </c>
+      <c r="U24" t="s">
+        <v>568</v>
+      </c>
+      <c r="V24" t="s">
+        <v>319</v>
+      </c>
+      <c r="W24" t="s">
+        <v>345</v>
+      </c>
+      <c r="X24" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>322</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>344</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>347</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>325</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>346</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>356</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>359</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>343</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>578</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>579</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>927</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>928</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>580</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>581</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>583</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>584</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>341</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>342</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>358</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>320</v>
+      </c>
+      <c r="AS24" t="s">
+        <v>929</v>
+      </c>
+      <c r="AT24" t="s">
+        <v>930</v>
+      </c>
+      <c r="AU24" t="s">
+        <v>357</v>
+      </c>
+      <c r="AV24" t="s">
+        <v>565</v>
+      </c>
+      <c r="AW24" t="s">
+        <v>591</v>
+      </c>
+      <c r="AX24" t="s">
+        <v>569</v>
+      </c>
+      <c r="AY24" t="s">
+        <v>593</v>
+      </c>
+      <c r="AZ24" t="s">
+        <v>324</v>
+      </c>
+      <c r="BA24" t="s">
+        <v>323</v>
+      </c>
+      <c r="BB24" t="s">
+        <v>329</v>
+      </c>
+      <c r="BC24" t="s">
+        <v>328</v>
+      </c>
+      <c r="BE24" t="s">
         <v>367</v>
       </c>
-      <c r="I24" t="s">
-        <v>118</v>
-      </c>
-      <c r="J24" t="s">
-        <v>118</v>
-      </c>
-      <c r="K24" t="s">
-        <v>1072</v>
-      </c>
-      <c r="L24" t="s">
-        <v>1073</v>
-      </c>
-      <c r="M24" s="3">
-        <v>32</v>
-      </c>
-      <c r="N24" s="3">
-        <v>68</v>
-      </c>
-      <c r="O24" t="s">
+      <c r="BF24" t="s">
+        <v>368</v>
+      </c>
+      <c r="BG24" t="s">
+        <v>163</v>
+      </c>
+      <c r="BH24" t="s">
+        <v>598</v>
+      </c>
+      <c r="BI24" t="s">
+        <v>365</v>
+      </c>
+      <c r="BJ24">
+        <v>2.8</v>
+      </c>
+      <c r="BK24">
+        <v>2.8</v>
+      </c>
+      <c r="BL24">
+        <v>2.8</v>
+      </c>
+      <c r="BN24" t="s">
+        <v>594</v>
+      </c>
+      <c r="BO24" t="s">
+        <v>595</v>
+      </c>
+      <c r="BP24" t="s">
+        <v>596</v>
+      </c>
+      <c r="BQ24" t="s">
         <v>371</v>
       </c>
-      <c r="P24" t="s">
-        <v>435</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>109</v>
-      </c>
-      <c r="R24" t="s">
-        <v>114</v>
-      </c>
-      <c r="S24" t="s">
-        <v>114</v>
-      </c>
-      <c r="T24" t="s">
-        <v>114</v>
-      </c>
-      <c r="U24" t="s">
-        <v>180</v>
-      </c>
-      <c r="V24" t="s">
-        <v>371</v>
-      </c>
-      <c r="W24" t="s">
-        <v>1074</v>
-      </c>
-      <c r="X24" t="s">
-        <v>1075</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>1076</v>
-      </c>
-      <c r="Z24" t="s">
-        <v>1077</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>114</v>
-      </c>
-      <c r="AB24" t="s">
-        <v>118</v>
-      </c>
-      <c r="AC24" t="s">
-        <v>495</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>1004</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>1078</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>945</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>629</v>
-      </c>
-      <c r="AH24" t="s">
-        <v>631</v>
-      </c>
-      <c r="AI24" t="s">
-        <v>632</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>633</v>
-      </c>
-      <c r="AK24" t="s">
-        <v>630</v>
-      </c>
-      <c r="AL24" t="s">
-        <v>636</v>
-      </c>
-      <c r="AM24" t="s">
-        <v>662</v>
-      </c>
-      <c r="AN24" t="s">
-        <v>634</v>
-      </c>
-      <c r="AO24" t="s">
-        <v>637</v>
-      </c>
-      <c r="AP24" t="s">
-        <v>659</v>
-      </c>
-      <c r="AQ24" t="s">
-        <v>638</v>
-      </c>
-      <c r="AR24" t="s">
-        <v>377</v>
-      </c>
-      <c r="AS24" t="s">
-        <v>403</v>
-      </c>
-      <c r="AT24" t="s">
-        <v>379</v>
-      </c>
-      <c r="AU24" t="s">
-        <v>380</v>
-      </c>
-      <c r="AV24" t="s">
-        <v>402</v>
-      </c>
-      <c r="AW24" t="s">
-        <v>405</v>
-      </c>
-      <c r="AX24" t="s">
-        <v>383</v>
-      </c>
-      <c r="AY24" t="s">
-        <v>404</v>
-      </c>
-      <c r="AZ24" t="s">
-        <v>414</v>
-      </c>
-      <c r="BA24" t="s">
-        <v>417</v>
-      </c>
-      <c r="BB24" t="s">
-        <v>401</v>
-      </c>
-      <c r="BC24" t="s">
-        <v>648</v>
-      </c>
-      <c r="BD24" t="s">
-        <v>649</v>
-      </c>
-      <c r="BE24" t="s">
-        <v>1079</v>
-      </c>
-      <c r="BF24" t="s">
-        <v>1080</v>
-      </c>
-      <c r="BG24" t="s">
-        <v>650</v>
-      </c>
-      <c r="BH24" t="s">
-        <v>651</v>
-      </c>
-      <c r="BI24" t="s">
-        <v>653</v>
-      </c>
-      <c r="BJ24" t="s">
-        <v>654</v>
-      </c>
-      <c r="BK24" t="s">
-        <v>399</v>
-      </c>
-      <c r="BL24" t="s">
-        <v>400</v>
-      </c>
-      <c r="BM24" t="s">
-        <v>416</v>
-      </c>
-      <c r="BN24" t="s">
-        <v>378</v>
-      </c>
-      <c r="BO24" t="s">
-        <v>1081</v>
-      </c>
-      <c r="BP24" t="s">
-        <v>1082</v>
-      </c>
-      <c r="BQ24" t="s">
-        <v>415</v>
-      </c>
-      <c r="BR24" t="s">
-        <v>635</v>
-      </c>
       <c r="BS24" t="s">
-        <v>661</v>
-      </c>
-      <c r="BT24" t="s">
-        <v>639</v>
-      </c>
-      <c r="BU24" t="s">
-        <v>663</v>
-      </c>
-      <c r="BV24" t="s">
-        <v>382</v>
-      </c>
-      <c r="BW24" t="s">
-        <v>381</v>
-      </c>
-      <c r="BX24" t="s">
-        <v>387</v>
-      </c>
-      <c r="BY24" t="s">
-        <v>386</v>
-      </c>
-      <c r="CA24" t="s">
-        <v>425</v>
-      </c>
-      <c r="CB24" t="s">
-        <v>426</v>
-      </c>
-      <c r="CC24" t="s">
-        <v>204</v>
-      </c>
-      <c r="CD24" t="s">
-        <v>668</v>
-      </c>
-      <c r="CE24" t="s">
-        <v>423</v>
-      </c>
-      <c r="CF24">
-        <v>2.8</v>
-      </c>
-      <c r="CG24">
-        <v>2.8</v>
-      </c>
-      <c r="CH24">
-        <v>2.8</v>
-      </c>
-      <c r="CJ24" t="s">
-        <v>664</v>
-      </c>
-      <c r="CK24" t="s">
-        <v>665</v>
-      </c>
-      <c r="CL24" t="s">
-        <v>666</v>
-      </c>
-      <c r="CM24" t="s">
-        <v>429</v>
-      </c>
-      <c r="CO24" t="s">
-        <v>406</v>
+        <v>348</v>
       </c>
     </row>
-    <row r="25" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:75" x14ac:dyDescent="0.2">
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:75" x14ac:dyDescent="0.2">
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:75" x14ac:dyDescent="0.2">
       <c r="F27" s="2"/>
     </row>
-    <row r="28" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:75" x14ac:dyDescent="0.2">
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:75" x14ac:dyDescent="0.2">
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:75" x14ac:dyDescent="0.2">
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:75" x14ac:dyDescent="0.2">
       <c r="F31" s="2"/>
     </row>
-    <row r="32" spans="1:97" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:75" x14ac:dyDescent="0.2">
       <c r="F32" s="2"/>
     </row>
     <row r="33" spans="6:6" x14ac:dyDescent="0.2">
